--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucil\Desktop\pagina RMKITS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313F8E89-A6B7-4147-897D-073BBC4E9624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C50192D-FC4C-4E6E-91EE-3EA89B668CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3670" yWindow="0" windowWidth="4840" windowHeight="9740" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -90,9 +90,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Lapiz negro grafito Filgo HB (unidad)</t>
-  </si>
-  <si>
     <t>Corrector liquido Filgo 012 (unidad)</t>
   </si>
   <si>
@@ -910,6 +907,9 @@
   </si>
   <si>
     <t>Papel glase fluo sobre x5 hojas</t>
+  </si>
+  <si>
+    <t>Hola</t>
   </si>
 </sst>
 </file>
@@ -984,7 +984,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -994,6 +994,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1308,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B0D8A5A-108C-466C-953C-70B57E87E4C5}">
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:K133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.1796875" customWidth="1"/>
@@ -1317,7 +1318,7 @@
     <col min="9" max="9" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1343,15 +1344,15 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>291</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
@@ -1372,15 +1373,15 @@
         <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>17</v>
@@ -1401,15 +1402,15 @@
         <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -1430,15 +1431,15 @@
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -1459,15 +1460,15 @@
         <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
         <v>17</v>
@@ -1485,18 +1486,18 @@
         <v>567</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>17</v>
@@ -1514,18 +1515,18 @@
         <v>3454</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
@@ -1543,18 +1544,18 @@
         <v>5464675</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -1572,18 +1573,18 @@
         <v>4545</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -1601,18 +1602,18 @@
         <v>3463</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
@@ -1630,18 +1631,19 @@
         <v>3463</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
@@ -1659,18 +1661,18 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
         <v>17</v>
@@ -1688,18 +1690,18 @@
         <v>3463</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
         <v>17</v>
@@ -1717,18 +1719,18 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
         <v>17</v>
@@ -1746,18 +1748,18 @@
         <v>3463</v>
       </c>
       <c r="H15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
         <v>17</v>
@@ -1775,18 +1777,18 @@
         <v>3463</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
         <v>17</v>
@@ -1808,15 +1810,15 @@
         <v>A0018.jpg</v>
       </c>
       <c r="I17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
         <v>17</v>
@@ -1838,15 +1840,15 @@
         <v>A0019.jpg</v>
       </c>
       <c r="I18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" t="s">
         <v>17</v>
@@ -1868,15 +1870,15 @@
         <v>A0020.jpg</v>
       </c>
       <c r="I19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
         <v>17</v>
@@ -1898,15 +1900,15 @@
         <v>A0021.jpg</v>
       </c>
       <c r="I20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
         <v>17</v>
@@ -1928,15 +1930,15 @@
         <v>A0045.jpg</v>
       </c>
       <c r="I21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
@@ -1954,19 +1956,19 @@
         <v>3463</v>
       </c>
       <c r="H22" t="str">
-        <f>_xlfn.CONCAT(A22,".jpg")</f>
+        <f t="shared" ref="H22:H32" si="1">_xlfn.CONCAT(A22,".jpg")</f>
         <v>A0016.jpg</v>
       </c>
       <c r="I22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -1984,19 +1986,19 @@
         <v>3463</v>
       </c>
       <c r="H23" t="str">
-        <f>_xlfn.CONCAT(A23,".jpg")</f>
+        <f t="shared" si="1"/>
         <v>A0017.jpg</v>
       </c>
       <c r="I23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
         <v>17</v>
@@ -2014,19 +2016,19 @@
         <v>200</v>
       </c>
       <c r="H24" t="str">
-        <f>_xlfn.CONCAT(A24,".jpg")</f>
+        <f t="shared" si="1"/>
         <v>A0022.jpg</v>
       </c>
       <c r="I24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
         <v>17</v>
@@ -2044,19 +2046,19 @@
         <v>200</v>
       </c>
       <c r="H25" t="str">
-        <f>_xlfn.CONCAT(A25,".jpg")</f>
+        <f t="shared" si="1"/>
         <v>A0023.jpg</v>
       </c>
       <c r="I25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
         <v>17</v>
@@ -2074,19 +2076,19 @@
         <v>200</v>
       </c>
       <c r="H26" t="str">
-        <f>_xlfn.CONCAT(A26,".jpg")</f>
+        <f t="shared" si="1"/>
         <v>A0024.jpg</v>
       </c>
       <c r="I26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
@@ -2104,19 +2106,19 @@
         <v>200</v>
       </c>
       <c r="H27" t="str">
-        <f>_xlfn.CONCAT(A27,".jpg")</f>
+        <f t="shared" si="1"/>
         <v>A0025.jpg</v>
       </c>
       <c r="I27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
         <v>17</v>
@@ -2134,19 +2136,19 @@
         <v>200</v>
       </c>
       <c r="H28" t="str">
-        <f>_xlfn.CONCAT(A28,".jpg")</f>
+        <f t="shared" si="1"/>
         <v>A0026.jpg</v>
       </c>
       <c r="I28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
         <v>17</v>
@@ -2164,19 +2166,19 @@
         <v>200</v>
       </c>
       <c r="H29" t="str">
-        <f>_xlfn.CONCAT(A29,".jpg")</f>
+        <f t="shared" si="1"/>
         <v>A0027.jpg</v>
       </c>
       <c r="I29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
         <v>17</v>
@@ -2194,19 +2196,19 @@
         <v>200</v>
       </c>
       <c r="H30" t="str">
-        <f>_xlfn.CONCAT(A30,".jpg")</f>
+        <f t="shared" si="1"/>
         <v>A0028.jpg</v>
       </c>
       <c r="I30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" t="s">
         <v>17</v>
@@ -2224,19 +2226,19 @@
         <v>200</v>
       </c>
       <c r="H31" t="str">
-        <f>_xlfn.CONCAT(A31,".jpg")</f>
+        <f t="shared" si="1"/>
         <v>A0029.jpg</v>
       </c>
       <c r="I31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
         <v>17</v>
@@ -2254,19 +2256,19 @@
         <v>200</v>
       </c>
       <c r="H32" t="str">
-        <f>_xlfn.CONCAT(A32,".jpg")</f>
+        <f t="shared" si="1"/>
         <v>A0030.jpg</v>
       </c>
       <c r="I32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
         <v>17</v>
@@ -2284,19 +2286,19 @@
         <v>200</v>
       </c>
       <c r="H33" t="str">
-        <f t="shared" ref="H33:H95" si="1">_xlfn.CONCAT(A33,".jpg")</f>
+        <f t="shared" ref="H33:H95" si="2">_xlfn.CONCAT(A33,".jpg")</f>
         <v>A0031.jpg</v>
       </c>
       <c r="I33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
         <v>17</v>
@@ -2314,19 +2316,19 @@
         <v>200</v>
       </c>
       <c r="H34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0032.jpg</v>
       </c>
       <c r="I34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
         <v>17</v>
@@ -2344,19 +2346,19 @@
         <v>200</v>
       </c>
       <c r="H35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0033.jpg</v>
       </c>
       <c r="I35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
         <v>17</v>
@@ -2374,19 +2376,19 @@
         <v>0</v>
       </c>
       <c r="H36" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0034.jpg</v>
       </c>
       <c r="I36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
         <v>17</v>
@@ -2404,19 +2406,19 @@
         <v>300</v>
       </c>
       <c r="H37" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0035.jpg</v>
       </c>
       <c r="I37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
         <v>17</v>
@@ -2434,19 +2436,19 @@
         <v>300</v>
       </c>
       <c r="H38" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0036.jpg</v>
       </c>
       <c r="I38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
         <v>17</v>
@@ -2464,19 +2466,19 @@
         <v>300</v>
       </c>
       <c r="H39" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0037.jpg</v>
       </c>
       <c r="I39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
         <v>17</v>
@@ -2494,19 +2496,19 @@
         <v>300</v>
       </c>
       <c r="H40" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0038.jpg</v>
       </c>
       <c r="I40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
         <v>17</v>
@@ -2524,19 +2526,19 @@
         <v>300</v>
       </c>
       <c r="H41" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0039.jpg</v>
       </c>
       <c r="I41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
         <v>17</v>
@@ -2554,19 +2556,19 @@
         <v>300</v>
       </c>
       <c r="H42" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0040.jpg</v>
       </c>
       <c r="I42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
         <v>17</v>
@@ -2584,19 +2586,19 @@
         <v>300</v>
       </c>
       <c r="H43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0041.jpg</v>
       </c>
       <c r="I43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
         <v>17</v>
@@ -2614,19 +2616,19 @@
         <v>300</v>
       </c>
       <c r="H44" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0042.jpg</v>
       </c>
       <c r="I44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B45" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
         <v>17</v>
@@ -2644,19 +2646,19 @@
         <v>300</v>
       </c>
       <c r="H45" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0043.jpg</v>
       </c>
       <c r="I45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
         <v>17</v>
@@ -2674,19 +2676,19 @@
         <v>300</v>
       </c>
       <c r="H46" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0044.jpg</v>
       </c>
       <c r="I46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="2">
@@ -2702,19 +2704,19 @@
         <v>300</v>
       </c>
       <c r="H47" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0046.jpg</v>
       </c>
       <c r="I47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="2">
@@ -2730,19 +2732,19 @@
         <v>300</v>
       </c>
       <c r="H48" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0047.jpg</v>
       </c>
       <c r="I48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>17</v>
@@ -2760,19 +2762,19 @@
         <v>300</v>
       </c>
       <c r="H49" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0048.jpg</v>
       </c>
       <c r="I49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>17</v>
@@ -2790,19 +2792,19 @@
         <v>300</v>
       </c>
       <c r="H50" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0049.jpg</v>
       </c>
       <c r="I50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>17</v>
@@ -2820,19 +2822,19 @@
         <v>300</v>
       </c>
       <c r="H51" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0050.jpg</v>
       </c>
       <c r="I51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>17</v>
@@ -2850,19 +2852,19 @@
         <v>300</v>
       </c>
       <c r="H52" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0051.jpg</v>
       </c>
       <c r="I52" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>17</v>
@@ -2880,19 +2882,19 @@
         <v>300</v>
       </c>
       <c r="H53" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0052.jpg</v>
       </c>
       <c r="I53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>17</v>
@@ -2910,19 +2912,19 @@
         <v>300</v>
       </c>
       <c r="H54" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0053.jpg</v>
       </c>
       <c r="I54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>17</v>
@@ -2940,19 +2942,19 @@
         <v>300</v>
       </c>
       <c r="H55" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0054.jpg</v>
       </c>
       <c r="I55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>17</v>
@@ -2970,19 +2972,19 @@
         <v>300</v>
       </c>
       <c r="H56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0055.jpg</v>
       </c>
       <c r="I56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>17</v>
@@ -3000,19 +3002,19 @@
         <v>300</v>
       </c>
       <c r="H57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0056.jpg</v>
       </c>
       <c r="I57" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>17</v>
@@ -3030,19 +3032,19 @@
         <v>300</v>
       </c>
       <c r="H58" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0057.jpg</v>
       </c>
       <c r="I58" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>17</v>
@@ -3060,19 +3062,19 @@
         <v>300</v>
       </c>
       <c r="H59" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0058.jpg</v>
       </c>
       <c r="I59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>17</v>
@@ -3090,19 +3092,19 @@
         <v>300</v>
       </c>
       <c r="H60" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0059.jpg</v>
       </c>
       <c r="I60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>17</v>
@@ -3120,19 +3122,19 @@
         <v>300</v>
       </c>
       <c r="H61" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0060.jpg</v>
       </c>
       <c r="I61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>17</v>
@@ -3150,19 +3152,19 @@
         <v>300</v>
       </c>
       <c r="H62" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0061.jpg</v>
       </c>
       <c r="I62" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>17</v>
@@ -3180,19 +3182,19 @@
         <v>300</v>
       </c>
       <c r="H63" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0062.jpg</v>
       </c>
       <c r="I63" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>17</v>
@@ -3210,19 +3212,19 @@
         <v>300</v>
       </c>
       <c r="H64" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0063.jpg</v>
       </c>
       <c r="I64" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>17</v>
@@ -3240,19 +3242,19 @@
         <v>300</v>
       </c>
       <c r="H65" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0064.jpg</v>
       </c>
       <c r="I65" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>17</v>
@@ -3270,19 +3272,19 @@
         <v>300</v>
       </c>
       <c r="H66" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0065.jpg</v>
       </c>
       <c r="I66" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>17</v>
@@ -3300,19 +3302,19 @@
         <v>300</v>
       </c>
       <c r="H67" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0066.jpg</v>
       </c>
       <c r="I67" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>17</v>
@@ -3330,19 +3332,19 @@
         <v>300</v>
       </c>
       <c r="H68" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0067.jpg</v>
       </c>
       <c r="I68" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>17</v>
@@ -3358,19 +3360,19 @@
         <v>300</v>
       </c>
       <c r="H69" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0068.jpg</v>
       </c>
       <c r="I69" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>17</v>
@@ -3388,19 +3390,19 @@
         <v>300</v>
       </c>
       <c r="H70" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0069.jpg</v>
       </c>
       <c r="I70" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>17</v>
@@ -3418,19 +3420,19 @@
         <v>300</v>
       </c>
       <c r="H71" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0070.jpg</v>
       </c>
       <c r="I71" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>17</v>
@@ -3448,19 +3450,19 @@
         <v>300</v>
       </c>
       <c r="H72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0071.jpg</v>
       </c>
       <c r="I72" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>17</v>
@@ -3478,19 +3480,19 @@
         <v>300</v>
       </c>
       <c r="H73" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0072.jpg</v>
       </c>
       <c r="I73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>17</v>
@@ -3508,19 +3510,19 @@
         <v>300</v>
       </c>
       <c r="H74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0073.jpg</v>
       </c>
       <c r="I74" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>17</v>
@@ -3538,19 +3540,19 @@
         <v>300</v>
       </c>
       <c r="H75" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0074.jpg</v>
       </c>
       <c r="I75" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>17</v>
@@ -3568,19 +3570,19 @@
         <v>300</v>
       </c>
       <c r="H76" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0075.jpg</v>
       </c>
       <c r="I76" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>17</v>
@@ -3598,19 +3600,19 @@
         <v>300</v>
       </c>
       <c r="H77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0076.jpg</v>
       </c>
       <c r="I77" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>17</v>
@@ -3628,19 +3630,19 @@
         <v>300</v>
       </c>
       <c r="H78" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0077.jpg</v>
       </c>
       <c r="I78" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>17</v>
@@ -3658,19 +3660,19 @@
         <v>300</v>
       </c>
       <c r="H79" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0078.jpg</v>
       </c>
       <c r="I79" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>17</v>
@@ -3688,19 +3690,19 @@
         <v>300</v>
       </c>
       <c r="H80" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0079.jpg</v>
       </c>
       <c r="I80" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>17</v>
@@ -3718,19 +3720,19 @@
         <v>300</v>
       </c>
       <c r="H81" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0080.jpg</v>
       </c>
       <c r="I81" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>17</v>
@@ -3748,19 +3750,19 @@
         <v>300</v>
       </c>
       <c r="H82" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0081.jpg</v>
       </c>
       <c r="I82" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>17</v>
@@ -3778,19 +3780,19 @@
         <v>300</v>
       </c>
       <c r="H83" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0082.jpg</v>
       </c>
       <c r="I83" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>17</v>
@@ -3808,19 +3810,19 @@
         <v>300</v>
       </c>
       <c r="H84" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0083.jpg</v>
       </c>
       <c r="I84" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>17</v>
@@ -3838,19 +3840,19 @@
         <v>300</v>
       </c>
       <c r="H85" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0084.jpg</v>
       </c>
       <c r="I85" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>17</v>
@@ -3868,19 +3870,19 @@
         <v>300</v>
       </c>
       <c r="H86" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0085.jpg</v>
       </c>
       <c r="I86" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>17</v>
@@ -3898,19 +3900,19 @@
         <v>300</v>
       </c>
       <c r="H87" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0086.jpg</v>
       </c>
       <c r="I87" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>17</v>
@@ -3928,19 +3930,19 @@
         <v>300</v>
       </c>
       <c r="H88" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0087.jpg</v>
       </c>
       <c r="I88" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>17</v>
@@ -3958,19 +3960,19 @@
         <v>300</v>
       </c>
       <c r="H89" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0088.jpg</v>
       </c>
       <c r="I89" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="2">
@@ -3986,19 +3988,19 @@
         <v>300</v>
       </c>
       <c r="H90" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0089.jpg</v>
       </c>
       <c r="I90" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="2">
@@ -4014,19 +4016,19 @@
         <v>300</v>
       </c>
       <c r="H91" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0090.jpg</v>
       </c>
       <c r="I91" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="2">
@@ -4042,19 +4044,19 @@
         <v>300</v>
       </c>
       <c r="H92" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0091.jpg</v>
       </c>
       <c r="I92" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="2">
@@ -4070,19 +4072,19 @@
         <v>300</v>
       </c>
       <c r="H93" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0092.jpg</v>
       </c>
       <c r="I93" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="2">
@@ -4098,19 +4100,19 @@
         <v>300</v>
       </c>
       <c r="H94" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0093.jpg</v>
       </c>
       <c r="I94" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="2">
@@ -4126,19 +4128,19 @@
         <v>300</v>
       </c>
       <c r="H95" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>A0094.jpg</v>
       </c>
       <c r="I95" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="2">
@@ -4154,19 +4156,19 @@
         <v>300</v>
       </c>
       <c r="H96" t="str">
-        <f t="shared" ref="H96:H133" si="2">_xlfn.CONCAT(A96,".jpg")</f>
+        <f t="shared" ref="H96:H133" si="3">_xlfn.CONCAT(A96,".jpg")</f>
         <v>A0095.jpg</v>
       </c>
       <c r="I96" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>17</v>
@@ -4184,19 +4186,19 @@
         <v>300</v>
       </c>
       <c r="H97" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0096.jpg</v>
       </c>
       <c r="I97" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>17</v>
@@ -4214,19 +4216,19 @@
         <v>300</v>
       </c>
       <c r="H98" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0097.jpg</v>
       </c>
       <c r="I98" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>17</v>
@@ -4244,19 +4246,19 @@
         <v>300</v>
       </c>
       <c r="H99" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0098.jpg</v>
       </c>
       <c r="I99" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>17</v>
@@ -4274,19 +4276,19 @@
         <v>300</v>
       </c>
       <c r="H100" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0099.jpg</v>
       </c>
       <c r="I100" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>17</v>
@@ -4304,19 +4306,19 @@
         <v>300</v>
       </c>
       <c r="H101" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0100.jpg</v>
       </c>
       <c r="I101" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>17</v>
@@ -4334,19 +4336,19 @@
         <v>300</v>
       </c>
       <c r="H102" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0101.jpg</v>
       </c>
       <c r="I102" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>17</v>
@@ -4364,19 +4366,19 @@
         <v>300</v>
       </c>
       <c r="H103" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0102.jpg</v>
       </c>
       <c r="I103" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>17</v>
@@ -4394,19 +4396,19 @@
         <v>300</v>
       </c>
       <c r="H104" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0103.jpg</v>
       </c>
       <c r="I104" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>17</v>
@@ -4424,19 +4426,19 @@
         <v>300</v>
       </c>
       <c r="H105" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0104.jpg</v>
       </c>
       <c r="I105" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>17</v>
@@ -4454,19 +4456,19 @@
         <v>300</v>
       </c>
       <c r="H106" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0105.jpg</v>
       </c>
       <c r="I106" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>17</v>
@@ -4484,19 +4486,19 @@
         <v>300</v>
       </c>
       <c r="H107" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0106.jpg</v>
       </c>
       <c r="I107" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>17</v>
@@ -4514,19 +4516,19 @@
         <v>300</v>
       </c>
       <c r="H108" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0107.jpg</v>
       </c>
       <c r="I108" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>17</v>
@@ -4544,19 +4546,19 @@
         <v>300</v>
       </c>
       <c r="H109" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0108.jpg</v>
       </c>
       <c r="I109" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>17</v>
@@ -4574,19 +4576,19 @@
         <v>300</v>
       </c>
       <c r="H110" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0109.jpg</v>
       </c>
       <c r="I110" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>17</v>
@@ -4604,19 +4606,19 @@
         <v>300</v>
       </c>
       <c r="H111" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0110.jpg</v>
       </c>
       <c r="I111" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>17</v>
@@ -4634,19 +4636,19 @@
         <v>300</v>
       </c>
       <c r="H112" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0111.jpg</v>
       </c>
       <c r="I112" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>17</v>
@@ -4664,19 +4666,19 @@
         <v>300</v>
       </c>
       <c r="H113" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0112.jpg</v>
       </c>
       <c r="I113" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>17</v>
@@ -4694,19 +4696,19 @@
         <v>300</v>
       </c>
       <c r="H114" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0113.jpg</v>
       </c>
       <c r="I114" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>17</v>
@@ -4724,19 +4726,19 @@
         <v>300</v>
       </c>
       <c r="H115" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0114.jpg</v>
       </c>
       <c r="I115" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>17</v>
@@ -4754,19 +4756,19 @@
         <v>300</v>
       </c>
       <c r="H116" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0115.jpg</v>
       </c>
       <c r="I116" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>17</v>
@@ -4784,19 +4786,19 @@
         <v>300</v>
       </c>
       <c r="H117" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0116.jpg</v>
       </c>
       <c r="I117" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>17</v>
@@ -4814,19 +4816,19 @@
         <v>300</v>
       </c>
       <c r="H118" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0117.jpg</v>
       </c>
       <c r="I118" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>17</v>
@@ -4844,19 +4846,19 @@
         <v>300</v>
       </c>
       <c r="H119" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0118.jpg</v>
       </c>
       <c r="I119" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>17</v>
@@ -4874,19 +4876,19 @@
         <v>300</v>
       </c>
       <c r="H120" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0119.jpg</v>
       </c>
       <c r="I120" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>17</v>
@@ -4904,19 +4906,19 @@
         <v>300</v>
       </c>
       <c r="H121" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0120.jpg</v>
       </c>
       <c r="I121" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>17</v>
@@ -4934,19 +4936,19 @@
         <v>300</v>
       </c>
       <c r="H122" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0121.jpg</v>
       </c>
       <c r="I122" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>17</v>
@@ -4964,19 +4966,19 @@
         <v>300</v>
       </c>
       <c r="H123" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0122.jpg</v>
       </c>
       <c r="I123" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>17</v>
@@ -4994,19 +4996,19 @@
         <v>300</v>
       </c>
       <c r="H124" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0123.jpg</v>
       </c>
       <c r="I124" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>17</v>
@@ -5024,19 +5026,19 @@
         <v>300</v>
       </c>
       <c r="H125" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0124.jpg</v>
       </c>
       <c r="I125" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>17</v>
@@ -5054,19 +5056,19 @@
         <v>300</v>
       </c>
       <c r="H126" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0125.jpg</v>
       </c>
       <c r="I126" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>17</v>
@@ -5084,19 +5086,19 @@
         <v>300</v>
       </c>
       <c r="H127" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0126.jpg</v>
       </c>
       <c r="I127" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>17</v>
@@ -5114,19 +5116,19 @@
         <v>300</v>
       </c>
       <c r="H128" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0127.jpg</v>
       </c>
       <c r="I128" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>17</v>
@@ -5144,19 +5146,19 @@
         <v>300</v>
       </c>
       <c r="H129" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0128.jpg</v>
       </c>
       <c r="I129" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>17</v>
@@ -5174,19 +5176,19 @@
         <v>300</v>
       </c>
       <c r="H130" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0129.jpg</v>
       </c>
       <c r="I130" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>17</v>
@@ -5204,19 +5206,19 @@
         <v>300</v>
       </c>
       <c r="H131" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0130.jpg</v>
       </c>
       <c r="I131" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>17</v>
@@ -5234,19 +5236,19 @@
         <v>300</v>
       </c>
       <c r="H132" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0131.jpg</v>
       </c>
       <c r="I132" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>17</v>
@@ -5264,11 +5266,11 @@
         <v>300</v>
       </c>
       <c r="H133" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>A0132.jpg</v>
       </c>
       <c r="I133" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucil\Desktop\pagina RMKITS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C50192D-FC4C-4E6E-91EE-3EA89B668CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAC95F4-D5FC-4FF9-9EEC-B88C4237976A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
   </bookViews>
@@ -909,7 +909,7 @@
     <t>Papel glase fluo sobre x5 hojas</t>
   </si>
   <si>
-    <t>Hola</t>
+    <t>Lapiz negro grafito Filgo HB (unidad)</t>
   </si>
 </sst>
 </file>
@@ -984,7 +984,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -994,7 +994,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1309,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B0D8A5A-108C-466C-953C-70B57E87E4C5}">
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.1796875" customWidth="1"/>
@@ -1318,7 +1317,7 @@
     <col min="9" max="9" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1347,7 +1346,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1376,7 +1375,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -1405,7 +1404,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -1434,7 +1433,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -1463,7 +1462,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -1492,7 +1491,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
@@ -1521,7 +1520,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
@@ -1550,7 +1549,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>23</v>
       </c>
@@ -1579,7 +1578,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
@@ -1608,7 +1607,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
@@ -1636,9 +1635,8 @@
       <c r="I11" t="s">
         <v>49</v>
       </c>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
@@ -1667,7 +1665,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
@@ -1696,7 +1694,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
@@ -1725,7 +1723,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>69</v>
       </c>
@@ -1754,7 +1752,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>70</v>
       </c>
@@ -3219,7 +3217,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="3" t="s">
         <v>212</v>
       </c>
@@ -3249,7 +3247,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="3" t="s">
         <v>213</v>
       </c>
@@ -3279,7 +3277,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="3" t="s">
         <v>214</v>
       </c>
@@ -3937,7 +3935,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="3" t="s">
         <v>236</v>
       </c>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucil\Desktop\pagina RMKITS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAC95F4-D5FC-4FF9-9EEC-B88C4237976A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F145DA7-0DAB-4AE0-8768-8FF1B71852CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
   </bookViews>
@@ -486,15 +486,9 @@
     <t>Mini Linternas</t>
   </si>
   <si>
-    <t>Viboras de goma</t>
-  </si>
-  <si>
     <t>Lapices Flexibles</t>
   </si>
   <si>
-    <t>Titeres de dedos</t>
-  </si>
-  <si>
     <t>Rompecabezas Diseños Surtidos</t>
   </si>
   <si>
@@ -510,12 +504,6 @@
     <t>Valija Jugar y Colorear con Librito y Lapices</t>
   </si>
   <si>
-    <t>Muñeco lanza canica</t>
-  </si>
-  <si>
-    <t>Tatuajes temporales infantiles</t>
-  </si>
-  <si>
     <t>Burbujero Dino/Pony</t>
   </si>
   <si>
@@ -531,45 +519,15 @@
     <t>Perrito que camina y ladra</t>
   </si>
   <si>
-    <t>Lapices cortos chinos x6 colores</t>
-  </si>
-  <si>
-    <t>Crayon chino x12 colores</t>
-  </si>
-  <si>
-    <t>Crayon chino x6 colores</t>
-  </si>
-  <si>
-    <t>Cuaderno Universitario Potosi t/flexible rayado 80 hojas</t>
-  </si>
-  <si>
-    <t>Cuaderno Universitario Potosi t/flexible cuadriculado 80 hojas</t>
-  </si>
-  <si>
-    <t>Cuaderno tapa flexible rayado 24 hojas</t>
-  </si>
-  <si>
-    <t>Cuaderno tapa flexible rayado 48 hojas</t>
-  </si>
-  <si>
     <t>Bolígrafo ABC tinta azul</t>
   </si>
   <si>
     <t>Bolígrafo ABC tinta negra</t>
   </si>
   <si>
-    <t>Sacapuntas plástico</t>
-  </si>
-  <si>
-    <t>Sacapuntas metálico</t>
-  </si>
-  <si>
     <t>Goma Katana Tinta y Lapiz</t>
   </si>
   <si>
-    <t>Tijera</t>
-  </si>
-  <si>
     <t>Marcador Permanente economico</t>
   </si>
   <si>
@@ -582,39 +540,12 @@
     <t>Set Geometria</t>
   </si>
   <si>
-    <t>Marcador Permanente doble punta</t>
-  </si>
-  <si>
-    <t>Adhesivo vinilico 30g</t>
-  </si>
-  <si>
-    <t>Adhesivo Sintético 30g</t>
-  </si>
-  <si>
     <t>Block de hojas color N5 x20 hojas Triunfante</t>
   </si>
   <si>
     <t>Block de hojas blanco N5 x20 hojas Triunfante</t>
   </si>
   <si>
-    <t>Canson N3 blanco</t>
-  </si>
-  <si>
-    <t>Canson N3 color</t>
-  </si>
-  <si>
-    <t>Canson n5 blanco</t>
-  </si>
-  <si>
-    <t>canson n5 color</t>
-  </si>
-  <si>
-    <t>cinta de papel 24mm</t>
-  </si>
-  <si>
-    <t>Regla mandala</t>
-  </si>
-  <si>
     <t>Microfibra filgo x10</t>
   </si>
   <si>
@@ -894,12 +825,6 @@
     <t>Plastilina Tintoretto x10 barritas</t>
   </si>
   <si>
-    <t>cinta de embalar 90 mts</t>
-  </si>
-  <si>
-    <t>cinta de embalar 40 mts</t>
-  </si>
-  <si>
     <t>Papel glase metalizado sobre x10 hojas</t>
   </si>
   <si>
@@ -910,6 +835,81 @@
   </si>
   <si>
     <t>Lapiz negro grafito Filgo HB (unidad)</t>
+  </si>
+  <si>
+    <t>Repuesto Canson N°5 Color x6 hojas</t>
+  </si>
+  <si>
+    <t>Repuesto Canson N°5 Blanco x8 hojas</t>
+  </si>
+  <si>
+    <t>Repuesto Canson N°3 Blanco x8 hojas</t>
+  </si>
+  <si>
+    <t>Repuesto Canson N°3 Color x6 hojas</t>
+  </si>
+  <si>
+    <t>Cinta de papel 24mm</t>
+  </si>
+  <si>
+    <t>Cinta de embalar 90 mts</t>
+  </si>
+  <si>
+    <t>Cinta de embalar 40 mts</t>
+  </si>
+  <si>
+    <t>Regla Mandala Espirógrafo</t>
+  </si>
+  <si>
+    <t>Adhesivo Vinilico Tintoretto 30g</t>
+  </si>
+  <si>
+    <t>Adhesivo Sintético Tintoretto 30g</t>
+  </si>
+  <si>
+    <t>Marcador Permanente doble punta economico</t>
+  </si>
+  <si>
+    <t>Tijera Plastica Filo Metal</t>
+  </si>
+  <si>
+    <t>Sacapuntas Metálico</t>
+  </si>
+  <si>
+    <t>Sacapuntas Plástico</t>
+  </si>
+  <si>
+    <t>Cuaderno tapa flexible rayado x24 hojas</t>
+  </si>
+  <si>
+    <t>Cuaderno tapa flexible rayado x48 hojas</t>
+  </si>
+  <si>
+    <t>Cuaderno Universitario Potosi t/flexible Rayado x80 hojas</t>
+  </si>
+  <si>
+    <t>Cuaderno Universitario Potosi t/flexible Cuadriculado x80 hojas</t>
+  </si>
+  <si>
+    <t>Crayones Economicos x12 colores</t>
+  </si>
+  <si>
+    <t>Crayones Economicos x6 colores</t>
+  </si>
+  <si>
+    <t>Lapices Cortos Chinos x6 colores</t>
+  </si>
+  <si>
+    <t>Muñeco Lanza Canica</t>
+  </si>
+  <si>
+    <t>Tatuajes Temporales Infantiles</t>
+  </si>
+  <si>
+    <t>Titeres de Dedos</t>
+  </si>
+  <si>
+    <t>Viboras de Goma</t>
   </si>
 </sst>
 </file>
@@ -937,7 +937,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -956,8 +956,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -980,11 +986,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -994,6 +1028,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1321,28 +1373,28 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="7" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1350,28 +1402,28 @@
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>12</v>
-      </c>
-      <c r="G2">
+      <c r="D2" s="7">
+        <v>50</v>
+      </c>
+      <c r="E2" s="7">
+        <v>12</v>
+      </c>
+      <c r="F2" s="7">
+        <v>12</v>
+      </c>
+      <c r="G2" s="7">
         <v>100000</v>
       </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1379,28 +1431,28 @@
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="7">
         <v>250</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="7">
         <v>24</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="7">
         <v>24</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="7">
         <v>100000</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1408,28 +1460,28 @@
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="7">
         <v>0</v>
       </c>
-      <c r="E4">
-        <v>12</v>
-      </c>
-      <c r="F4">
-        <v>12</v>
-      </c>
-      <c r="G4">
+      <c r="E4" s="7">
+        <v>12</v>
+      </c>
+      <c r="F4" s="7">
+        <v>12</v>
+      </c>
+      <c r="G4" s="7">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1437,28 +1489,28 @@
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5">
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7">
         <v>900</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="7">
         <v>30</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="7">
         <v>30</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="7">
         <v>546</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1466,28 +1518,28 @@
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6">
+      <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="7">
         <v>600</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="7">
         <v>30</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="7">
         <v>30</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="7">
         <v>567</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1495,28 +1547,28 @@
       <c r="A7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7">
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7">
         <v>80</v>
       </c>
-      <c r="E7">
-        <v>50</v>
-      </c>
-      <c r="F7">
-        <v>50</v>
-      </c>
-      <c r="G7">
+      <c r="E7" s="7">
+        <v>50</v>
+      </c>
+      <c r="F7" s="7">
+        <v>50</v>
+      </c>
+      <c r="G7" s="7">
         <v>3454</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1524,28 +1576,28 @@
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8">
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7">
         <v>80</v>
       </c>
-      <c r="E8">
-        <v>50</v>
-      </c>
-      <c r="F8">
-        <v>50</v>
-      </c>
-      <c r="G8">
+      <c r="E8" s="7">
+        <v>50</v>
+      </c>
+      <c r="F8" s="7">
+        <v>50</v>
+      </c>
+      <c r="G8" s="7">
         <v>5464675</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1553,28 +1605,28 @@
       <c r="A9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9">
-        <v>300</v>
-      </c>
-      <c r="E9">
+      <c r="C9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7">
+        <v>300</v>
+      </c>
+      <c r="E9" s="7">
         <v>36</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>36</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="7">
         <v>4545</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1582,28 +1634,28 @@
       <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10">
-        <v>300</v>
-      </c>
-      <c r="E10">
+      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="7">
+        <v>300</v>
+      </c>
+      <c r="E10" s="7">
         <v>36</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="7">
         <v>36</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="7">
         <v>3463</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1611,28 +1663,28 @@
       <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11">
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="7">
         <v>650</v>
       </c>
-      <c r="E11">
-        <v>12</v>
-      </c>
-      <c r="F11">
-        <v>12</v>
-      </c>
-      <c r="G11">
+      <c r="E11" s="7">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7">
+        <v>12</v>
+      </c>
+      <c r="G11" s="7">
         <v>3463</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1640,28 +1692,28 @@
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12">
+      <c r="C12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="7">
         <v>0</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="7">
         <v>6</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>6</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="7">
         <v>0</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1669,28 +1721,28 @@
       <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13">
+      <c r="C13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="7">
         <v>3000</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="7">
         <v>6</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="7">
         <v>6</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="7">
         <v>3463</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1698,28 +1750,28 @@
       <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7">
         <v>0</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="7">
         <v>3</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="7">
         <v>3</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="7">
         <v>0</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1727,28 +1779,28 @@
       <c r="A15" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15">
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7">
         <v>285</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="7">
         <v>24</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="7">
         <v>24</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="7">
         <v>3463</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1756,28 +1808,28 @@
       <c r="A16" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16">
+      <c r="C16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7">
         <v>500</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="7">
         <v>24</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>24</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="7">
         <v>3463</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1785,29 +1837,29 @@
       <c r="A17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17">
+      <c r="C17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="7">
         <v>1800</v>
       </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17">
+      <c r="E17" s="11">
+        <v>12</v>
+      </c>
+      <c r="F17" s="11">
+        <v>12</v>
+      </c>
+      <c r="G17" s="7">
         <v>200</v>
       </c>
-      <c r="H17" t="str">
+      <c r="H17" s="7" t="str">
         <f>_xlfn.CONCAT(A17,".jpg")</f>
         <v>A0018.jpg</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1815,29 +1867,29 @@
       <c r="A18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18">
+      <c r="C18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="7">
         <v>1800</v>
       </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
+      <c r="E18" s="11">
+        <v>12</v>
+      </c>
+      <c r="F18" s="11">
+        <v>12</v>
+      </c>
+      <c r="G18" s="7">
         <v>200</v>
       </c>
-      <c r="H18" t="str">
+      <c r="H18" s="7" t="str">
         <f t="shared" ref="H18:H21" si="0">_xlfn.CONCAT(A18,".jpg")</f>
         <v>A0019.jpg</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1845,29 +1897,29 @@
       <c r="A19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19">
+      <c r="C19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="7">
         <v>2500</v>
       </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
+      <c r="E19" s="11">
+        <v>12</v>
+      </c>
+      <c r="F19" s="11">
+        <v>12</v>
+      </c>
+      <c r="G19" s="7">
         <v>200</v>
       </c>
-      <c r="H19" t="str">
+      <c r="H19" s="7" t="str">
         <f t="shared" si="0"/>
         <v>A0020.jpg</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1875,29 +1927,29 @@
       <c r="A20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20">
+      <c r="C20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7">
         <v>4600</v>
       </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20">
+      <c r="E20" s="11">
+        <v>6</v>
+      </c>
+      <c r="F20" s="11">
+        <v>6</v>
+      </c>
+      <c r="G20" s="7">
         <v>200</v>
       </c>
-      <c r="H20" t="str">
+      <c r="H20" s="7" t="str">
         <f t="shared" si="0"/>
         <v>A0021.jpg</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1905,29 +1957,29 @@
       <c r="A21" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21">
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7">
         <v>950</v>
       </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
+      <c r="E21" s="11">
+        <v>12</v>
+      </c>
+      <c r="F21" s="11">
+        <v>12</v>
+      </c>
+      <c r="G21" s="7">
         <v>200</v>
       </c>
-      <c r="H21" t="str">
+      <c r="H21" s="7" t="str">
         <f t="shared" si="0"/>
         <v>A0045.jpg</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1935,29 +1987,29 @@
       <c r="A22" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22">
+      <c r="C22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="7">
         <v>450</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="11">
         <v>24</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="11">
         <v>24</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="7">
         <v>3463</v>
       </c>
-      <c r="H22" t="str">
+      <c r="H22" s="7" t="str">
         <f t="shared" ref="H22:H32" si="1">_xlfn.CONCAT(A22,".jpg")</f>
         <v>A0016.jpg</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1965,29 +2017,29 @@
       <c r="A23" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23">
+      <c r="C23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="7">
         <v>600</v>
       </c>
-      <c r="E23">
-        <v>12</v>
-      </c>
-      <c r="F23">
-        <v>12</v>
-      </c>
-      <c r="G23">
+      <c r="E23" s="11">
+        <v>12</v>
+      </c>
+      <c r="F23" s="11">
+        <v>12</v>
+      </c>
+      <c r="G23" s="7">
         <v>3463</v>
       </c>
-      <c r="H23" t="str">
+      <c r="H23" s="7" t="str">
         <f t="shared" si="1"/>
         <v>A0017.jpg</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1995,29 +2047,29 @@
       <c r="A24" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24">
+      <c r="C24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="7">
         <v>1400</v>
       </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
+      <c r="E24" s="11">
+        <v>12</v>
+      </c>
+      <c r="F24" s="11">
+        <v>12</v>
+      </c>
+      <c r="G24" s="7">
         <v>200</v>
       </c>
-      <c r="H24" t="str">
+      <c r="H24" s="7" t="str">
         <f t="shared" si="1"/>
         <v>A0022.jpg</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2025,29 +2077,29 @@
       <c r="A25" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25">
+      <c r="C25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="7">
         <v>2500</v>
       </c>
-      <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
+      <c r="E25" s="11">
+        <v>12</v>
+      </c>
+      <c r="F25" s="11">
+        <v>12</v>
+      </c>
+      <c r="G25" s="7">
         <v>200</v>
       </c>
-      <c r="H25" t="str">
+      <c r="H25" s="7" t="str">
         <f t="shared" si="1"/>
         <v>A0023.jpg</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2055,29 +2107,29 @@
       <c r="A26" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26">
+      <c r="C26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="7">
         <v>4600</v>
       </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
+      <c r="E26" s="11">
+        <v>12</v>
+      </c>
+      <c r="F26" s="11">
+        <v>12</v>
+      </c>
+      <c r="G26" s="7">
         <v>200</v>
       </c>
-      <c r="H26" t="str">
+      <c r="H26" s="7" t="str">
         <f t="shared" si="1"/>
         <v>A0024.jpg</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2085,29 +2137,29 @@
       <c r="A27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C27" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27">
+      <c r="C27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="7">
         <v>13500</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="11">
+        <v>12</v>
+      </c>
+      <c r="F27" s="11">
         <v>1</v>
       </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
+      <c r="G27" s="7">
         <v>200</v>
       </c>
-      <c r="H27" t="str">
+      <c r="H27" s="7" t="str">
         <f t="shared" si="1"/>
         <v>A0025.jpg</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2115,29 +2167,29 @@
       <c r="A28" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28">
+      <c r="C28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="7">
         <v>23000</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="11">
+        <v>8</v>
+      </c>
+      <c r="F28" s="11">
         <v>1</v>
       </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
+      <c r="G28" s="7">
         <v>200</v>
       </c>
-      <c r="H28" t="str">
+      <c r="H28" s="7" t="str">
         <f t="shared" si="1"/>
         <v>A0026.jpg</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2145,29 +2197,29 @@
       <c r="A29" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C29" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29">
+      <c r="C29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="7">
         <v>32500</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="11">
+        <v>6</v>
+      </c>
+      <c r="F29" s="11">
         <v>1</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
+      <c r="G29" s="7">
         <v>200</v>
       </c>
-      <c r="H29" t="str">
+      <c r="H29" s="7" t="str">
         <f t="shared" si="1"/>
         <v>A0027.jpg</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2175,29 +2227,29 @@
       <c r="A30" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30">
+      <c r="C30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="7">
         <v>43800</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="11">
+        <v>3</v>
+      </c>
+      <c r="F30" s="11">
         <v>1</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30">
+      <c r="G30" s="7">
         <v>200</v>
       </c>
-      <c r="H30" t="str">
+      <c r="H30" s="7" t="str">
         <f t="shared" si="1"/>
         <v>A0028.jpg</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2205,29 +2257,29 @@
       <c r="A31" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31">
+      <c r="C31" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="7">
         <v>600</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="11">
+        <v>12</v>
+      </c>
+      <c r="F31" s="11">
         <v>1</v>
       </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31">
+      <c r="G31" s="7">
         <v>200</v>
       </c>
-      <c r="H31" t="str">
+      <c r="H31" s="7" t="str">
         <f t="shared" si="1"/>
         <v>A0029.jpg</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2235,29 +2287,29 @@
       <c r="A32" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C32" t="s">
-        <v>17</v>
-      </c>
-      <c r="D32">
+      <c r="C32" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="7">
         <v>6480</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="11">
         <v>1</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="11">
         <v>1</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="7">
         <v>200</v>
       </c>
-      <c r="H32" t="str">
+      <c r="H32" s="7" t="str">
         <f t="shared" si="1"/>
         <v>A0030.jpg</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2265,29 +2317,29 @@
       <c r="A33" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C33" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33">
+      <c r="C33" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="7">
         <v>6480</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="11">
         <v>1</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="11">
         <v>1</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="7">
         <v>200</v>
       </c>
-      <c r="H33" t="str">
+      <c r="H33" s="7" t="str">
         <f t="shared" ref="H33:H95" si="2">_xlfn.CONCAT(A33,".jpg")</f>
         <v>A0031.jpg</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2295,29 +2347,29 @@
       <c r="A34" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C34" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34">
+      <c r="C34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="7">
         <v>370</v>
       </c>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34">
+      <c r="E34" s="11">
+        <v>24</v>
+      </c>
+      <c r="F34" s="11">
+        <v>24</v>
+      </c>
+      <c r="G34" s="7">
         <v>200</v>
       </c>
-      <c r="H34" t="str">
+      <c r="H34" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0032.jpg</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2325,29 +2377,29 @@
       <c r="A35" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35">
+      <c r="C35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="7">
         <v>700</v>
       </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35">
+      <c r="E35" s="11">
+        <v>24</v>
+      </c>
+      <c r="F35" s="11">
+        <v>24</v>
+      </c>
+      <c r="G35" s="7">
         <v>200</v>
       </c>
-      <c r="H35" t="str">
+      <c r="H35" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0033.jpg</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2355,29 +2407,29 @@
       <c r="A36" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C36" t="s">
-        <v>17</v>
-      </c>
-      <c r="D36">
+      <c r="C36" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="7">
         <v>0</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="10">
         <v>1</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="10">
         <v>1</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="7">
         <v>0</v>
       </c>
-      <c r="H36" t="str">
+      <c r="H36" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0034.jpg</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2385,29 +2437,29 @@
       <c r="A37" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C37" t="s">
-        <v>17</v>
-      </c>
-      <c r="D37">
+      <c r="C37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="7">
         <v>190</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="7">
         <v>36</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="7">
         <v>36</v>
       </c>
-      <c r="G37">
-        <v>300</v>
-      </c>
-      <c r="H37" t="str">
+      <c r="G37" s="7">
+        <v>300</v>
+      </c>
+      <c r="H37" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0035.jpg</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2415,29 +2467,29 @@
       <c r="A38" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C38" t="s">
-        <v>17</v>
-      </c>
-      <c r="D38">
+      <c r="C38" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="7">
         <v>130</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="7">
         <v>36</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="7">
         <v>36</v>
       </c>
-      <c r="G38">
-        <v>300</v>
-      </c>
-      <c r="H38" t="str">
+      <c r="G38" s="7">
+        <v>300</v>
+      </c>
+      <c r="H38" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0036.jpg</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2445,29 +2497,29 @@
       <c r="A39" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C39" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39">
+      <c r="C39" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="7">
         <v>1300</v>
       </c>
-      <c r="E39">
-        <v>12</v>
-      </c>
-      <c r="F39">
-        <v>12</v>
-      </c>
-      <c r="G39">
-        <v>300</v>
-      </c>
-      <c r="H39" t="str">
+      <c r="E39" s="7">
+        <v>12</v>
+      </c>
+      <c r="F39" s="7">
+        <v>12</v>
+      </c>
+      <c r="G39" s="7">
+        <v>300</v>
+      </c>
+      <c r="H39" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0037.jpg</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2475,29 +2527,29 @@
       <c r="A40" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C40" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40">
-        <v>50</v>
-      </c>
-      <c r="E40">
+      <c r="C40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="7">
+        <v>50</v>
+      </c>
+      <c r="E40" s="7">
         <v>72</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="7">
         <v>72</v>
       </c>
-      <c r="G40">
-        <v>300</v>
-      </c>
-      <c r="H40" t="str">
+      <c r="G40" s="7">
+        <v>300</v>
+      </c>
+      <c r="H40" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0038.jpg</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2505,29 +2557,29 @@
       <c r="A41" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C41" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41">
+      <c r="C41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="7">
         <v>350</v>
       </c>
-      <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41">
-        <v>300</v>
-      </c>
-      <c r="H41" t="str">
+      <c r="E41" s="11">
+        <v>12</v>
+      </c>
+      <c r="F41" s="11">
+        <v>12</v>
+      </c>
+      <c r="G41" s="7">
+        <v>300</v>
+      </c>
+      <c r="H41" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0039.jpg</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2535,29 +2587,29 @@
       <c r="A42" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C42" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42">
+      <c r="C42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="7">
         <v>485</v>
       </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42">
-        <v>300</v>
-      </c>
-      <c r="H42" t="str">
+      <c r="E42" s="11">
+        <v>24</v>
+      </c>
+      <c r="F42" s="11">
+        <v>24</v>
+      </c>
+      <c r="G42" s="7">
+        <v>300</v>
+      </c>
+      <c r="H42" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0040.jpg</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2565,29 +2617,29 @@
       <c r="A43" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="C43" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43">
+      <c r="C43" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="7">
         <v>550</v>
       </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
-      <c r="G43">
-        <v>300</v>
-      </c>
-      <c r="H43" t="str">
+      <c r="E43" s="11">
+        <v>24</v>
+      </c>
+      <c r="F43" s="11">
+        <v>24</v>
+      </c>
+      <c r="G43" s="7">
+        <v>300</v>
+      </c>
+      <c r="H43" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0041.jpg</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2595,29 +2647,29 @@
       <c r="A44" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C44" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44">
+      <c r="C44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="7">
         <v>1800</v>
       </c>
-      <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
-      <c r="G44">
-        <v>300</v>
-      </c>
-      <c r="H44" t="str">
+      <c r="E44" s="11">
+        <v>12</v>
+      </c>
+      <c r="F44" s="11">
+        <v>12</v>
+      </c>
+      <c r="G44" s="7">
+        <v>300</v>
+      </c>
+      <c r="H44" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0042.jpg</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="7" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2625,823 +2677,823 @@
       <c r="A45" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C45" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45">
+      <c r="C45" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="7">
         <v>500</v>
       </c>
-      <c r="E45">
-        <v>1</v>
-      </c>
-      <c r="F45">
-        <v>1</v>
-      </c>
-      <c r="G45">
-        <v>300</v>
-      </c>
-      <c r="H45" t="str">
+      <c r="E45" s="11">
+        <v>12</v>
+      </c>
+      <c r="F45" s="11">
+        <v>12</v>
+      </c>
+      <c r="G45" s="7">
+        <v>300</v>
+      </c>
+      <c r="H45" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0043.jpg</v>
       </c>
-      <c r="I45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I45" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C46" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46">
+      <c r="C46" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="7">
         <v>350</v>
       </c>
-      <c r="E46">
-        <v>1</v>
-      </c>
-      <c r="F46">
-        <v>1</v>
-      </c>
-      <c r="G46">
-        <v>300</v>
-      </c>
-      <c r="H46" t="str">
+      <c r="E46" s="11">
+        <v>12</v>
+      </c>
+      <c r="F46" s="11">
+        <v>12</v>
+      </c>
+      <c r="G46" s="7">
+        <v>300</v>
+      </c>
+      <c r="H46" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0044.jpg</v>
       </c>
-      <c r="I46" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I46" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="9">
+        <v>3700</v>
+      </c>
+      <c r="E47" s="12">
+        <v>12</v>
+      </c>
+      <c r="F47" s="12">
+        <v>12</v>
+      </c>
+      <c r="G47" s="7">
+        <v>300</v>
+      </c>
+      <c r="H47" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0046.jpg</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C48" s="8"/>
+      <c r="D48" s="9">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="9">
+        <v>30</v>
+      </c>
+      <c r="F48" s="9">
+        <v>30</v>
+      </c>
+      <c r="G48" s="7">
+        <v>300</v>
+      </c>
+      <c r="H48" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0047.jpg</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="9">
+        <v>100</v>
+      </c>
+      <c r="E49" s="9">
+        <v>144</v>
+      </c>
+      <c r="F49" s="9">
+        <v>144</v>
+      </c>
+      <c r="G49" s="7">
+        <v>300</v>
+      </c>
+      <c r="H49" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0048.jpg</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="9">
+        <v>160</v>
+      </c>
+      <c r="E50" s="9">
+        <v>100</v>
+      </c>
+      <c r="F50" s="9">
+        <v>100</v>
+      </c>
+      <c r="G50" s="7">
+        <v>300</v>
+      </c>
+      <c r="H50" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0049.jpg</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="9">
+        <v>750</v>
+      </c>
+      <c r="E51" s="9">
+        <v>24</v>
+      </c>
+      <c r="F51" s="9">
+        <v>24</v>
+      </c>
+      <c r="G51" s="7">
+        <v>300</v>
+      </c>
+      <c r="H51" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0050.jpg</v>
+      </c>
+      <c r="I51" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="9">
+        <v>90</v>
+      </c>
+      <c r="E52" s="9">
+        <v>20</v>
+      </c>
+      <c r="F52" s="9">
+        <v>20</v>
+      </c>
+      <c r="G52" s="7">
+        <v>300</v>
+      </c>
+      <c r="H52" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0051.jpg</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="9">
+        <v>400</v>
+      </c>
+      <c r="E53" s="9">
+        <v>12</v>
+      </c>
+      <c r="F53" s="9">
+        <v>12</v>
+      </c>
+      <c r="G53" s="7">
+        <v>300</v>
+      </c>
+      <c r="H53" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0052.jpg</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="9">
+        <v>400</v>
+      </c>
+      <c r="E54" s="9">
+        <v>12</v>
+      </c>
+      <c r="F54" s="9">
+        <v>12</v>
+      </c>
+      <c r="G54" s="7">
+        <v>300</v>
+      </c>
+      <c r="H54" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0053.jpg</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="9">
+        <v>400</v>
+      </c>
+      <c r="E55" s="9">
+        <v>24</v>
+      </c>
+      <c r="F55" s="9">
+        <v>1</v>
+      </c>
+      <c r="G55" s="7">
+        <v>300</v>
+      </c>
+      <c r="H55" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0054.jpg</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="9">
+        <v>1360</v>
+      </c>
+      <c r="E56" s="9">
+        <v>12</v>
+      </c>
+      <c r="F56" s="9">
+        <v>1</v>
+      </c>
+      <c r="G56" s="7">
+        <v>300</v>
+      </c>
+      <c r="H56" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0055.jpg</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="9">
+        <v>1700</v>
+      </c>
+      <c r="E57" s="9">
+        <v>12</v>
+      </c>
+      <c r="F57" s="9">
+        <v>1</v>
+      </c>
+      <c r="G57" s="7">
+        <v>300</v>
+      </c>
+      <c r="H57" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0056.jpg</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="9">
+        <v>780</v>
+      </c>
+      <c r="E58" s="9">
+        <v>12</v>
+      </c>
+      <c r="F58" s="9">
+        <v>1</v>
+      </c>
+      <c r="G58" s="7">
+        <v>300</v>
+      </c>
+      <c r="H58" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0057.jpg</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="9">
+        <v>780</v>
+      </c>
+      <c r="E59" s="9">
+        <v>12</v>
+      </c>
+      <c r="F59" s="9">
+        <v>1</v>
+      </c>
+      <c r="G59" s="7">
+        <v>300</v>
+      </c>
+      <c r="H59" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0058.jpg</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" s="9">
+        <v>780</v>
+      </c>
+      <c r="E60" s="9">
+        <v>12</v>
+      </c>
+      <c r="F60" s="9">
+        <v>1</v>
+      </c>
+      <c r="G60" s="7">
+        <v>300</v>
+      </c>
+      <c r="H60" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0059.jpg</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="9">
+        <v>400</v>
+      </c>
+      <c r="E61" s="9">
+        <v>12</v>
+      </c>
+      <c r="F61" s="9">
+        <v>12</v>
+      </c>
+      <c r="G61" s="7">
+        <v>300</v>
+      </c>
+      <c r="H61" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0060.jpg</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="9">
+        <v>2200</v>
+      </c>
+      <c r="E62" s="9">
+        <v>12</v>
+      </c>
+      <c r="F62" s="9">
+        <v>1</v>
+      </c>
+      <c r="G62" s="7">
+        <v>300</v>
+      </c>
+      <c r="H62" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0061.jpg</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" s="9">
+        <v>170</v>
+      </c>
+      <c r="E63" s="9">
+        <v>13</v>
+      </c>
+      <c r="F63" s="9">
+        <v>13</v>
+      </c>
+      <c r="G63" s="7">
+        <v>300</v>
+      </c>
+      <c r="H63" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0062.jpg</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" s="9">
+        <v>400</v>
+      </c>
+      <c r="E64" s="9">
+        <v>12</v>
+      </c>
+      <c r="F64" s="9">
+        <v>12</v>
+      </c>
+      <c r="G64" s="7">
+        <v>300</v>
+      </c>
+      <c r="H64" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0063.jpg</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" s="9">
+        <v>6500</v>
+      </c>
+      <c r="E65" s="9">
+        <v>5</v>
+      </c>
+      <c r="F65" s="9">
+        <v>1</v>
+      </c>
+      <c r="G65" s="7">
+        <v>300</v>
+      </c>
+      <c r="H65" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0064.jpg</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="9">
+        <v>6500</v>
+      </c>
+      <c r="E66" s="9">
+        <v>5</v>
+      </c>
+      <c r="F66" s="9">
+        <v>1</v>
+      </c>
+      <c r="G66" s="7">
+        <v>300</v>
+      </c>
+      <c r="H66" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0065.jpg</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="9">
+        <v>6500</v>
+      </c>
+      <c r="E67" s="9">
+        <v>5</v>
+      </c>
+      <c r="F67" s="9">
+        <v>1</v>
+      </c>
+      <c r="G67" s="7">
+        <v>300</v>
+      </c>
+      <c r="H67" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0066.jpg</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="9">
+        <v>2000</v>
+      </c>
+      <c r="E68" s="9">
+        <v>3</v>
+      </c>
+      <c r="F68" s="9">
+        <v>1</v>
+      </c>
+      <c r="G68" s="7">
+        <v>300</v>
+      </c>
+      <c r="H68" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0067.jpg</v>
+      </c>
+      <c r="I68" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="2">
-        <v>3700</v>
-      </c>
-      <c r="E47" s="2">
-        <v>12</v>
-      </c>
-      <c r="F47" s="2">
-        <v>12</v>
-      </c>
-      <c r="G47">
-        <v>300</v>
-      </c>
-      <c r="H47" t="str">
-        <f t="shared" si="2"/>
-        <v>A0046.jpg</v>
-      </c>
-      <c r="I47" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="3" t="s">
+      <c r="B69" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" s="8"/>
+      <c r="E69" s="9">
+        <v>3</v>
+      </c>
+      <c r="F69" s="9">
+        <v>1</v>
+      </c>
+      <c r="G69" s="7">
+        <v>300</v>
+      </c>
+      <c r="H69" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0068.jpg</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="9">
+        <v>200</v>
+      </c>
+      <c r="E70" s="9">
+        <v>20</v>
+      </c>
+      <c r="F70" s="9">
+        <v>20</v>
+      </c>
+      <c r="G70" s="7">
+        <v>300</v>
+      </c>
+      <c r="H70" s="7" t="str">
+        <f t="shared" si="2"/>
+        <v>A0069.jpg</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="2">
-        <v>1500</v>
-      </c>
-      <c r="E48" s="2">
-        <v>30</v>
-      </c>
-      <c r="F48" s="2">
-        <v>30</v>
-      </c>
-      <c r="G48">
-        <v>300</v>
-      </c>
-      <c r="H48" t="str">
-        <f t="shared" si="2"/>
-        <v>A0047.jpg</v>
-      </c>
-      <c r="I48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D49" s="2">
-        <v>100</v>
-      </c>
-      <c r="E49" s="2">
-        <v>144</v>
-      </c>
-      <c r="F49" s="2">
-        <v>144</v>
-      </c>
-      <c r="G49">
-        <v>300</v>
-      </c>
-      <c r="H49" t="str">
-        <f t="shared" si="2"/>
-        <v>A0048.jpg</v>
-      </c>
-      <c r="I49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="2">
-        <v>160</v>
-      </c>
-      <c r="E50" s="2">
-        <v>100</v>
-      </c>
-      <c r="F50" s="2">
-        <v>100</v>
-      </c>
-      <c r="G50">
-        <v>300</v>
-      </c>
-      <c r="H50" t="str">
-        <f t="shared" si="2"/>
-        <v>A0049.jpg</v>
-      </c>
-      <c r="I50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="2">
-        <v>750</v>
-      </c>
-      <c r="E51" s="2">
-        <v>24</v>
-      </c>
-      <c r="F51" s="2">
-        <v>24</v>
-      </c>
-      <c r="G51">
-        <v>300</v>
-      </c>
-      <c r="H51" t="str">
-        <f t="shared" si="2"/>
-        <v>A0050.jpg</v>
-      </c>
-      <c r="I51" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" s="2">
-        <v>90</v>
-      </c>
-      <c r="E52" s="2">
+      <c r="B71" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="9">
+        <v>200</v>
+      </c>
+      <c r="E71" s="9">
         <v>20</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F71" s="9">
         <v>20</v>
       </c>
-      <c r="G52">
-        <v>300</v>
-      </c>
-      <c r="H52" t="str">
-        <f t="shared" si="2"/>
-        <v>A0051.jpg</v>
-      </c>
-      <c r="I52" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="2">
-        <v>400</v>
-      </c>
-      <c r="E53" s="2">
-        <v>12</v>
-      </c>
-      <c r="F53" s="2">
-        <v>12</v>
-      </c>
-      <c r="G53">
-        <v>300</v>
-      </c>
-      <c r="H53" t="str">
-        <f t="shared" si="2"/>
-        <v>A0052.jpg</v>
-      </c>
-      <c r="I53" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" s="2">
-        <v>400</v>
-      </c>
-      <c r="E54" s="2">
-        <v>12</v>
-      </c>
-      <c r="F54" s="2">
-        <v>12</v>
-      </c>
-      <c r="G54">
-        <v>300</v>
-      </c>
-      <c r="H54" t="str">
-        <f t="shared" si="2"/>
-        <v>A0053.jpg</v>
-      </c>
-      <c r="I54" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D55" s="2">
-        <v>400</v>
-      </c>
-      <c r="E55" s="2">
-        <v>24</v>
-      </c>
-      <c r="F55" s="2">
-        <v>1</v>
-      </c>
-      <c r="G55">
-        <v>300</v>
-      </c>
-      <c r="H55" t="str">
-        <f t="shared" si="2"/>
-        <v>A0054.jpg</v>
-      </c>
-      <c r="I55" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" s="2">
-        <v>1360</v>
-      </c>
-      <c r="E56" s="2">
-        <v>12</v>
-      </c>
-      <c r="F56" s="2">
-        <v>1</v>
-      </c>
-      <c r="G56">
-        <v>300</v>
-      </c>
-      <c r="H56" t="str">
-        <f t="shared" si="2"/>
-        <v>A0055.jpg</v>
-      </c>
-      <c r="I56" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D57" s="2">
-        <v>1700</v>
-      </c>
-      <c r="E57" s="2">
-        <v>12</v>
-      </c>
-      <c r="F57" s="2">
-        <v>1</v>
-      </c>
-      <c r="G57">
-        <v>300</v>
-      </c>
-      <c r="H57" t="str">
-        <f t="shared" si="2"/>
-        <v>A0056.jpg</v>
-      </c>
-      <c r="I57" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D58" s="2">
-        <v>780</v>
-      </c>
-      <c r="E58" s="2">
-        <v>12</v>
-      </c>
-      <c r="F58" s="2">
-        <v>1</v>
-      </c>
-      <c r="G58">
-        <v>300</v>
-      </c>
-      <c r="H58" t="str">
-        <f t="shared" si="2"/>
-        <v>A0057.jpg</v>
-      </c>
-      <c r="I58" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D59" s="2">
-        <v>780</v>
-      </c>
-      <c r="E59" s="2">
-        <v>12</v>
-      </c>
-      <c r="F59" s="2">
-        <v>1</v>
-      </c>
-      <c r="G59">
-        <v>300</v>
-      </c>
-      <c r="H59" t="str">
-        <f t="shared" si="2"/>
-        <v>A0058.jpg</v>
-      </c>
-      <c r="I59" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" s="2">
-        <v>780</v>
-      </c>
-      <c r="E60" s="2">
-        <v>12</v>
-      </c>
-      <c r="F60" s="2">
-        <v>1</v>
-      </c>
-      <c r="G60">
-        <v>300</v>
-      </c>
-      <c r="H60" t="str">
-        <f t="shared" si="2"/>
-        <v>A0059.jpg</v>
-      </c>
-      <c r="I60" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" s="2">
-        <v>400</v>
-      </c>
-      <c r="E61" s="2">
-        <v>12</v>
-      </c>
-      <c r="F61" s="2">
-        <v>12</v>
-      </c>
-      <c r="G61">
-        <v>300</v>
-      </c>
-      <c r="H61" t="str">
-        <f t="shared" si="2"/>
-        <v>A0060.jpg</v>
-      </c>
-      <c r="I61" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D62" s="2">
-        <v>2200</v>
-      </c>
-      <c r="E62" s="2">
-        <v>12</v>
-      </c>
-      <c r="F62" s="2">
-        <v>1</v>
-      </c>
-      <c r="G62">
-        <v>300</v>
-      </c>
-      <c r="H62" t="str">
-        <f t="shared" si="2"/>
-        <v>A0061.jpg</v>
-      </c>
-      <c r="I62" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D63" s="2">
-        <v>170</v>
-      </c>
-      <c r="E63" s="2">
-        <v>13</v>
-      </c>
-      <c r="F63" s="2">
-        <v>13</v>
-      </c>
-      <c r="G63">
-        <v>300</v>
-      </c>
-      <c r="H63" t="str">
-        <f t="shared" si="2"/>
-        <v>A0062.jpg</v>
-      </c>
-      <c r="I63" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D64" s="2">
-        <v>400</v>
-      </c>
-      <c r="E64" s="2">
-        <v>12</v>
-      </c>
-      <c r="F64" s="2">
-        <v>12</v>
-      </c>
-      <c r="G64">
-        <v>300</v>
-      </c>
-      <c r="H64" t="str">
-        <f t="shared" si="2"/>
-        <v>A0063.jpg</v>
-      </c>
-      <c r="I64" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D65" s="2">
-        <v>6500</v>
-      </c>
-      <c r="E65" s="2">
-        <v>5</v>
-      </c>
-      <c r="F65" s="2">
-        <v>1</v>
-      </c>
-      <c r="G65">
-        <v>300</v>
-      </c>
-      <c r="H65" t="str">
-        <f t="shared" si="2"/>
-        <v>A0064.jpg</v>
-      </c>
-      <c r="I65" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" s="2">
-        <v>6500</v>
-      </c>
-      <c r="E66" s="2">
-        <v>5</v>
-      </c>
-      <c r="F66" s="2">
-        <v>1</v>
-      </c>
-      <c r="G66">
-        <v>300</v>
-      </c>
-      <c r="H66" t="str">
-        <f t="shared" si="2"/>
-        <v>A0065.jpg</v>
-      </c>
-      <c r="I66" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" s="2">
-        <v>6500</v>
-      </c>
-      <c r="E67" s="2">
-        <v>5</v>
-      </c>
-      <c r="F67" s="2">
-        <v>1</v>
-      </c>
-      <c r="G67">
-        <v>300</v>
-      </c>
-      <c r="H67" t="str">
-        <f t="shared" si="2"/>
-        <v>A0066.jpg</v>
-      </c>
-      <c r="I67" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" s="2">
-        <v>2000</v>
-      </c>
-      <c r="E68" s="2">
-        <v>3</v>
-      </c>
-      <c r="F68" s="2">
-        <v>1</v>
-      </c>
-      <c r="G68">
-        <v>300</v>
-      </c>
-      <c r="H68" t="str">
-        <f t="shared" si="2"/>
-        <v>A0067.jpg</v>
-      </c>
-      <c r="I68" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" s="1"/>
-      <c r="E69" s="2">
-        <v>3</v>
-      </c>
-      <c r="F69" s="2">
-        <v>1</v>
-      </c>
-      <c r="G69">
-        <v>300</v>
-      </c>
-      <c r="H69" t="str">
-        <f t="shared" si="2"/>
-        <v>A0068.jpg</v>
-      </c>
-      <c r="I69" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" s="2">
-        <v>200</v>
-      </c>
-      <c r="E70" s="2">
-        <v>20</v>
-      </c>
-      <c r="F70" s="2">
-        <v>20</v>
-      </c>
-      <c r="G70">
-        <v>300</v>
-      </c>
-      <c r="H70" t="str">
-        <f t="shared" si="2"/>
-        <v>A0069.jpg</v>
-      </c>
-      <c r="I70" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" s="2">
-        <v>200</v>
-      </c>
-      <c r="E71" s="2">
-        <v>20</v>
-      </c>
-      <c r="F71" s="2">
-        <v>20</v>
-      </c>
-      <c r="G71">
-        <v>300</v>
-      </c>
-      <c r="H71" t="str">
+      <c r="G71" s="7">
+        <v>300</v>
+      </c>
+      <c r="H71" s="7" t="str">
         <f t="shared" si="2"/>
         <v>A0070.jpg</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I71" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B72" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" s="2">
+      <c r="C72" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="6">
         <v>250</v>
       </c>
-      <c r="E72" s="2">
-        <v>50</v>
-      </c>
-      <c r="F72" s="2">
+      <c r="E72" s="6">
+        <v>50</v>
+      </c>
+      <c r="F72" s="6">
         <v>1</v>
       </c>
       <c r="G72">
@@ -3457,7 +3509,7 @@
     </row>
     <row r="73" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>141</v>
@@ -3487,7 +3539,7 @@
     </row>
     <row r="74" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>142</v>
@@ -3517,7 +3569,7 @@
     </row>
     <row r="75" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>143</v>
@@ -3547,7 +3599,7 @@
     </row>
     <row r="76" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="3" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>144</v>
@@ -3577,7 +3629,7 @@
     </row>
     <row r="77" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="3" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>145</v>
@@ -3607,7 +3659,7 @@
     </row>
     <row r="78" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="3" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>146</v>
@@ -3637,7 +3689,7 @@
     </row>
     <row r="79" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>147</v>
@@ -3667,7 +3719,7 @@
     </row>
     <row r="80" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="3" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>148</v>
@@ -3697,7 +3749,7 @@
     </row>
     <row r="81" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="3" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>149</v>
@@ -3727,10 +3779,10 @@
     </row>
     <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="3" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>150</v>
+        <v>291</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>17</v>
@@ -3757,10 +3809,10 @@
     </row>
     <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="3" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>17</v>
@@ -3787,10 +3839,10 @@
     </row>
     <row r="84" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="3" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>152</v>
+        <v>290</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>17</v>
@@ -3817,10 +3869,10 @@
     </row>
     <row r="85" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>17</v>
@@ -3847,10 +3899,10 @@
     </row>
     <row r="86" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3" t="s">
-        <v>233</v>
+        <v>210</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>17</v>
@@ -3877,10 +3929,10 @@
     </row>
     <row r="87" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="3" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>17</v>
@@ -3907,10 +3959,10 @@
     </row>
     <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="3" t="s">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>17</v>
@@ -3937,10 +3989,10 @@
     </row>
     <row r="89" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="3" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>17</v>
@@ -3967,10 +4019,10 @@
     </row>
     <row r="90" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="3" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>158</v>
+        <v>288</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="2">
@@ -3995,10 +4047,10 @@
     </row>
     <row r="91" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="3" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>159</v>
+        <v>289</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="2">
@@ -4023,10 +4075,10 @@
     </row>
     <row r="92" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="3" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="2">
@@ -4051,10 +4103,10 @@
     </row>
     <row r="93" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="3" t="s">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="2">
@@ -4079,10 +4131,10 @@
     </row>
     <row r="94" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="3" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="2">
@@ -4107,10 +4159,10 @@
     </row>
     <row r="95" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="3" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="2">
@@ -4135,10 +4187,10 @@
     </row>
     <row r="96" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="3" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="2">
@@ -4163,10 +4215,10 @@
     </row>
     <row r="97" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="3" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>165</v>
+        <v>287</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>17</v>
@@ -4193,10 +4245,10 @@
     </row>
     <row r="98" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="3" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>166</v>
+        <v>285</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>17</v>
@@ -4223,10 +4275,10 @@
     </row>
     <row r="99" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>167</v>
+        <v>286</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>17</v>
@@ -4253,10 +4305,10 @@
     </row>
     <row r="100" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3" t="s">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>168</v>
+        <v>283</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>17</v>
@@ -4283,10 +4335,10 @@
     </row>
     <row r="101" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>169</v>
+        <v>284</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>17</v>
@@ -4313,10 +4365,10 @@
     </row>
     <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>170</v>
+        <v>281</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>17</v>
@@ -4343,10 +4395,10 @@
     </row>
     <row r="103" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>171</v>
+        <v>282</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>17</v>
@@ -4373,10 +4425,10 @@
     </row>
     <row r="104" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>17</v>
@@ -4403,10 +4455,10 @@
     </row>
     <row r="105" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>17</v>
@@ -4433,10 +4485,10 @@
     </row>
     <row r="106" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>17</v>
@@ -4463,10 +4515,10 @@
     </row>
     <row r="107" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="3" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>17</v>
@@ -4493,10 +4545,10 @@
     </row>
     <row r="108" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>17</v>
@@ -4523,10 +4575,10 @@
     </row>
     <row r="109" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="3" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>177</v>
+        <v>278</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>17</v>
@@ -4553,10 +4605,10 @@
     </row>
     <row r="110" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="3" t="s">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>17</v>
@@ -4571,7 +4623,7 @@
         <v>10</v>
       </c>
       <c r="G110">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H110" t="str">
         <f t="shared" si="3"/>
@@ -4583,10 +4635,10 @@
     </row>
     <row r="111" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="3" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>17</v>
@@ -4613,10 +4665,10 @@
     </row>
     <row r="112" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>17</v>
@@ -4643,10 +4695,10 @@
     </row>
     <row r="113" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="3" t="s">
-        <v>260</v>
+        <v>237</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>17</v>
@@ -4673,10 +4725,10 @@
     </row>
     <row r="114" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>17</v>
@@ -4703,10 +4755,10 @@
     </row>
     <row r="115" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>17</v>
@@ -4733,10 +4785,10 @@
     </row>
     <row r="116" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3" t="s">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>17</v>
@@ -4763,10 +4815,10 @@
     </row>
     <row r="117" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
-        <v>264</v>
+        <v>241</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>17</v>
@@ -4793,10 +4845,10 @@
     </row>
     <row r="118" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="3" t="s">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>17</v>
@@ -4823,10 +4875,10 @@
     </row>
     <row r="119" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3" t="s">
-        <v>266</v>
+        <v>243</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>17</v>
@@ -4853,10 +4905,10 @@
     </row>
     <row r="120" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="3" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>17</v>
@@ -4883,10 +4935,10 @@
     </row>
     <row r="121" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>182</v>
+        <v>277</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>17</v>
@@ -4913,10 +4965,10 @@
     </row>
     <row r="122" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="3" t="s">
-        <v>269</v>
+        <v>246</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>183</v>
+        <v>275</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>17</v>
@@ -4943,10 +4995,10 @@
     </row>
     <row r="123" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="3" t="s">
-        <v>270</v>
+        <v>247</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>184</v>
+        <v>276</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>17</v>
@@ -4973,10 +5025,10 @@
     </row>
     <row r="124" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3" t="s">
-        <v>271</v>
+        <v>248</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>17</v>
@@ -4991,7 +5043,7 @@
         <v>10</v>
       </c>
       <c r="G124">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H124" t="str">
         <f t="shared" si="3"/>
@@ -5003,10 +5055,10 @@
     </row>
     <row r="125" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="3" t="s">
-        <v>272</v>
+        <v>249</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>17</v>
@@ -5021,7 +5073,7 @@
         <v>10</v>
       </c>
       <c r="G125">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H125" t="str">
         <f t="shared" si="3"/>
@@ -5033,10 +5085,10 @@
     </row>
     <row r="126" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="3" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>187</v>
+        <v>269</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>17</v>
@@ -5063,10 +5115,10 @@
     </row>
     <row r="127" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>17</v>
@@ -5093,10 +5145,10 @@
     </row>
     <row r="128" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>189</v>
+        <v>268</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>17</v>
@@ -5123,10 +5175,10 @@
     </row>
     <row r="129" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="3" t="s">
-        <v>276</v>
+        <v>253</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>190</v>
+        <v>267</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>17</v>
@@ -5153,10 +5205,10 @@
     </row>
     <row r="130" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="3" t="s">
-        <v>277</v>
+        <v>254</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>191</v>
+        <v>271</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>17</v>
@@ -5183,10 +5235,10 @@
     </row>
     <row r="131" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="3" t="s">
-        <v>278</v>
+        <v>255</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>17</v>
@@ -5213,10 +5265,10 @@
     </row>
     <row r="132" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="3" t="s">
-        <v>279</v>
+        <v>256</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>17</v>
@@ -5243,10 +5295,10 @@
     </row>
     <row r="133" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="3" t="s">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>192</v>
+        <v>274</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>17</v>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucil\Desktop\rmkits-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41261EF3-F30C-446C-835B-CD88391E9FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908B6534-5472-46C5-BCCC-6131A4C05627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="17380" windowHeight="7360" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="17390" windowHeight="7370" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1721,7 +1721,7 @@
         <v>6</v>
       </c>
       <c r="G12" s="5">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>43</v>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucil\Desktop\rmkits-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908B6534-5472-46C5-BCCC-6131A4C05627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD924234-E42B-4922-AC23-8A7E77B650CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="17390" windowHeight="7370" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
+    <workbookView xWindow="380" yWindow="0" windowWidth="18780" windowHeight="10200" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1035,7 +1035,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1058,6 +1058,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2899,7 +2902,7 @@
         <v>17</v>
       </c>
       <c r="D52" s="7">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="E52" s="7">
         <v>100</v>
@@ -2959,7 +2962,7 @@
         <v>17</v>
       </c>
       <c r="D54" s="7">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E54" s="7">
         <v>20</v>
@@ -2989,7 +2992,7 @@
         <v>17</v>
       </c>
       <c r="D55" s="7">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="E55" s="7">
         <v>12</v>
@@ -2998,7 +3001,7 @@
         <v>12</v>
       </c>
       <c r="G55" s="5">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H55" s="5" t="str">
         <f t="shared" si="0"/>
@@ -3019,7 +3022,7 @@
         <v>17</v>
       </c>
       <c r="D56" s="7">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="E56" s="7">
         <v>12</v>
@@ -3049,7 +3052,7 @@
         <v>17</v>
       </c>
       <c r="D57" s="7">
-        <v>400</v>
+        <v>510</v>
       </c>
       <c r="E57" s="7">
         <v>24</v>
@@ -3259,7 +3262,7 @@
         <v>17</v>
       </c>
       <c r="D64" s="7">
-        <v>2200</v>
+        <v>2500</v>
       </c>
       <c r="E64" s="7">
         <v>12</v>
@@ -3289,7 +3292,7 @@
         <v>17</v>
       </c>
       <c r="D65" s="7">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="E65" s="7">
         <v>12</v>
@@ -3499,7 +3502,7 @@
         <v>17</v>
       </c>
       <c r="D72" s="7">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E72" s="7">
         <v>20</v>
@@ -3529,7 +3532,7 @@
         <v>17</v>
       </c>
       <c r="D73" s="7">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E73" s="7">
         <v>20</v>
@@ -3649,7 +3652,7 @@
         <v>17</v>
       </c>
       <c r="D77" s="2">
-        <v>1100</v>
+        <v>1250</v>
       </c>
       <c r="E77" s="2">
         <v>12</v>
@@ -3679,7 +3682,7 @@
         <v>17</v>
       </c>
       <c r="D78" s="2">
-        <v>720</v>
+        <v>860</v>
       </c>
       <c r="E78" s="2">
         <v>12</v>
@@ -3769,7 +3772,7 @@
         <v>17</v>
       </c>
       <c r="D81" s="2">
-        <v>800</v>
+        <v>890</v>
       </c>
       <c r="E81" s="2">
         <v>12</v>
@@ -3799,7 +3802,7 @@
         <v>17</v>
       </c>
       <c r="D82" s="2">
-        <v>800</v>
+        <v>890</v>
       </c>
       <c r="E82" s="2">
         <v>12</v>
@@ -3829,7 +3832,7 @@
         <v>17</v>
       </c>
       <c r="D83" s="2">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="E83" s="2">
         <v>20</v>
@@ -3889,7 +3892,7 @@
         <v>17</v>
       </c>
       <c r="D85" s="2">
-        <v>930</v>
+        <v>1070</v>
       </c>
       <c r="E85" s="2">
         <v>12</v>
@@ -3919,7 +3922,7 @@
         <v>17</v>
       </c>
       <c r="D86" s="2">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
@@ -3972,14 +3975,14 @@
       <c r="A88" t="s">
         <v>201</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="9" t="s">
         <v>147</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D88" s="2">
-        <v>710</v>
+        <v>300</v>
       </c>
       <c r="E88" s="2">
         <v>12</v>
@@ -3988,7 +3991,7 @@
         <v>3</v>
       </c>
       <c r="G88">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="H88" t="str">
         <f t="shared" si="1"/>
@@ -4009,7 +4012,7 @@
         <v>17</v>
       </c>
       <c r="D89" s="2">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="E89" s="2">
         <v>12</v>
@@ -4039,7 +4042,7 @@
         <v>17</v>
       </c>
       <c r="D90" s="2">
-        <v>6300</v>
+        <v>7650</v>
       </c>
       <c r="E90" s="2">
         <v>1</v>
@@ -4078,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="G91">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H91" t="str">
         <f t="shared" si="1"/>
@@ -4127,7 +4130,7 @@
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="2">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="E93" s="2">
         <v>20</v>
@@ -4155,7 +4158,7 @@
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="2">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E94" s="2">
         <v>20</v>
@@ -4211,7 +4214,7 @@
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="2">
-        <v>5600</v>
+        <v>6120</v>
       </c>
       <c r="E96" s="2">
         <v>3</v>
@@ -4239,7 +4242,7 @@
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="2">
-        <v>5600</v>
+        <v>6120</v>
       </c>
       <c r="E97" s="2">
         <v>3</v>
@@ -4267,7 +4270,7 @@
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="2">
-        <v>5600</v>
+        <v>6120</v>
       </c>
       <c r="E98" s="2">
         <v>3</v>
@@ -4295,7 +4298,7 @@
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="2">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="E99" s="2">
         <v>3</v>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucil\Desktop\rmkits-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD924234-E42B-4922-AC23-8A7E77B650CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25564EA4-A796-44CA-913D-60037C28D03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="0" windowWidth="18780" windowHeight="10200" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
+    <workbookView xWindow="150" yWindow="1460" windowWidth="8860" windowHeight="9820" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="338">
   <si>
     <t>codigo</t>
   </si>
@@ -90,9 +90,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Corrector liquido Filgo 012 (unidad)</t>
-  </si>
-  <si>
     <t>Cinta correctora Filgo 12mts</t>
   </si>
   <si>
@@ -810,9 +807,6 @@
     <t>Papel glase fluo sobre x5 hojas</t>
   </si>
   <si>
-    <t>Lapiz negro grafito Filgo HB (unidad)</t>
-  </si>
-  <si>
     <t>Cinta de papel 24mm</t>
   </si>
   <si>
@@ -934,6 +928,126 @@
   </si>
   <si>
     <t>Repuesto Canson N°5 Color x6 hojas Triunfante</t>
+  </si>
+  <si>
+    <t>A0137</t>
+  </si>
+  <si>
+    <t>A0138</t>
+  </si>
+  <si>
+    <t>A0139</t>
+  </si>
+  <si>
+    <t>A0140</t>
+  </si>
+  <si>
+    <t>A0141</t>
+  </si>
+  <si>
+    <t>A0142</t>
+  </si>
+  <si>
+    <t>Puntero Láser colores pastel</t>
+  </si>
+  <si>
+    <t>Avion Planeador de Telgopor</t>
+  </si>
+  <si>
+    <t>Pollito Kawaii con ganchito</t>
+  </si>
+  <si>
+    <t>Soga de saltar infantil</t>
+  </si>
+  <si>
+    <t>Escarapela Argentina Moño</t>
+  </si>
+  <si>
+    <t>Escarapela Argentina Circular</t>
+  </si>
+  <si>
+    <t>Bandera Plástica 15x25 Argentina</t>
+  </si>
+  <si>
+    <t>A0143</t>
+  </si>
+  <si>
+    <t>A0144</t>
+  </si>
+  <si>
+    <t>A0145</t>
+  </si>
+  <si>
+    <t>A0146</t>
+  </si>
+  <si>
+    <t>A0147</t>
+  </si>
+  <si>
+    <t>Gusano Extensible</t>
+  </si>
+  <si>
+    <t>Lapiceras 4 colores en 1 unicornio</t>
+  </si>
+  <si>
+    <t>Silbatos</t>
+  </si>
+  <si>
+    <t>Portasube Colgante Colores Surtidos</t>
+  </si>
+  <si>
+    <t>Portasube Colgante Color Negro</t>
+  </si>
+  <si>
+    <t>A0148</t>
+  </si>
+  <si>
+    <t>Magic Snake Juego Ingenio</t>
+  </si>
+  <si>
+    <t>Masas Saltarinas PlayLife bolsa x15 masas</t>
+  </si>
+  <si>
+    <t>Capibara Squishy Yoyo con luz</t>
+  </si>
+  <si>
+    <t>Pelotitas Saltarinas</t>
+  </si>
+  <si>
+    <t>Tubo Plegable Antiestres con Luz</t>
+  </si>
+  <si>
+    <t>Copa del Mundo Alcancia Plastica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulseras Luminosas </t>
+  </si>
+  <si>
+    <t>A0149</t>
+  </si>
+  <si>
+    <t>A0150</t>
+  </si>
+  <si>
+    <t>A0151</t>
+  </si>
+  <si>
+    <t>A0152</t>
+  </si>
+  <si>
+    <t>A0153</t>
+  </si>
+  <si>
+    <t>A0154</t>
+  </si>
+  <si>
+    <t>A0155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapiz negro grafito Filgo HB </t>
+  </si>
+  <si>
+    <t>Corrector liquido Filgo 012</t>
   </si>
 </sst>
 </file>
@@ -961,15 +1075,21 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1031,11 +1151,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1062,6 +1191,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1376,7 +1521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B0D8A5A-108C-466C-953C-70B57E87E4C5}">
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.1796875" customWidth="1"/>
@@ -1411,7 +1556,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -1419,7 +1564,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>258</v>
+        <v>336</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>16</v>
@@ -1440,7 +1585,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -1448,7 +1593,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>18</v>
+        <v>337</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>17</v>
@@ -1469,7 +1614,7 @@
         <v>13</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -1477,7 +1622,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>17</v>
@@ -1498,7 +1643,7 @@
         <v>14</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
@@ -1506,7 +1651,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>17</v>
@@ -1527,15 +1672,15 @@
         <v>15</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>17</v>
@@ -1553,18 +1698,18 @@
         <v>500</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>17</v>
@@ -1582,18 +1727,18 @@
         <v>5000</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>17</v>
@@ -1611,18 +1756,18 @@
         <v>5000</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>17</v>
@@ -1640,18 +1785,18 @@
         <v>1500</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>17</v>
@@ -1669,18 +1814,18 @@
         <v>1500</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>17</v>
@@ -1698,18 +1843,18 @@
         <v>2400</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>17</v>
@@ -1727,18 +1872,18 @@
         <v>0</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>17</v>
@@ -1756,18 +1901,18 @@
         <v>120</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>17</v>
@@ -1785,18 +1930,18 @@
         <v>0</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>17</v>
@@ -1814,18 +1959,18 @@
         <v>2000</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>17</v>
@@ -1843,18 +1988,18 @@
         <v>2000</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>17</v>
@@ -1876,15 +2021,15 @@
         <v>A0018.jpg</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>17</v>
@@ -1906,15 +2051,15 @@
         <v>A0019.jpg</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>17</v>
@@ -1936,15 +2081,15 @@
         <v>A0020.jpg</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>17</v>
@@ -1966,15 +2111,15 @@
         <v>A0021.jpg</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>17</v>
@@ -1996,15 +2141,15 @@
         <v>A0045.jpg</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>17</v>
@@ -2026,15 +2171,15 @@
         <v>A0016.jpg</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>17</v>
@@ -2056,15 +2201,15 @@
         <v>A0017.jpg</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>17</v>
@@ -2086,15 +2231,15 @@
         <v>A0022.jpg</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>17</v>
@@ -2116,15 +2261,15 @@
         <v>A0023.jpg</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>17</v>
@@ -2146,15 +2291,15 @@
         <v>A0024.jpg</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>17</v>
@@ -2176,15 +2321,15 @@
         <v>A0025.jpg</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>17</v>
@@ -2206,15 +2351,15 @@
         <v>A0026.jpg</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>17</v>
@@ -2236,15 +2381,15 @@
         <v>A0027.jpg</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>17</v>
@@ -2266,15 +2411,15 @@
         <v>A0028.jpg</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>17</v>
@@ -2296,15 +2441,15 @@
         <v>A0029.jpg</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>17</v>
@@ -2326,15 +2471,15 @@
         <v>A0030.jpg</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>17</v>
@@ -2356,15 +2501,15 @@
         <v>A0031.jpg</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>17</v>
@@ -2386,15 +2531,15 @@
         <v>A0032.jpg</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>17</v>
@@ -2416,15 +2561,15 @@
         <v>A0033.jpg</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>17</v>
@@ -2446,15 +2591,15 @@
         <v>A0034.jpg</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>17</v>
@@ -2476,15 +2621,15 @@
         <v>A0035.jpg</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>17</v>
@@ -2506,15 +2651,15 @@
         <v>A0036.jpg</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>17</v>
@@ -2536,15 +2681,15 @@
         <v>A0037.jpg</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>17</v>
@@ -2566,15 +2711,15 @@
         <v>A0038.jpg</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>17</v>
@@ -2596,15 +2741,15 @@
         <v>A0039.jpg</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>17</v>
@@ -2626,15 +2771,15 @@
         <v>A0040.jpg</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>17</v>
@@ -2656,15 +2801,15 @@
         <v>A0041.jpg</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>17</v>
@@ -2686,15 +2831,15 @@
         <v>A0042.jpg</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5">
@@ -2714,15 +2859,15 @@
         <v>A0133.jpg</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5">
@@ -2742,15 +2887,15 @@
         <v>A0134.jpg</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>17</v>
@@ -2772,15 +2917,15 @@
         <v>A0043.jpg</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>17</v>
@@ -2802,15 +2947,15 @@
         <v>A0044.jpg</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="7">
@@ -2830,15 +2975,15 @@
         <v>A0046.jpg</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="7">
@@ -2858,15 +3003,15 @@
         <v>A0047.jpg</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>17</v>
@@ -2888,15 +3033,15 @@
         <v>A0048.jpg</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>17</v>
@@ -2918,15 +3063,15 @@
         <v>A0049.jpg</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>17</v>
@@ -2948,15 +3093,15 @@
         <v>A0050.jpg</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>17</v>
@@ -2978,15 +3123,15 @@
         <v>A0051.jpg</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>17</v>
@@ -3008,15 +3153,15 @@
         <v>A0052.jpg</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>17</v>
@@ -3038,15 +3183,15 @@
         <v>A0053.jpg</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>17</v>
@@ -3068,15 +3213,15 @@
         <v>A0054.jpg</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>17</v>
@@ -3098,15 +3243,15 @@
         <v>A0055.jpg</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="26" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>17</v>
@@ -3128,15 +3273,15 @@
         <v>A0056.jpg</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>17</v>
@@ -3158,15 +3303,15 @@
         <v>A0057.jpg</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>17</v>
@@ -3188,15 +3333,15 @@
         <v>A0058.jpg</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>17</v>
@@ -3218,15 +3363,15 @@
         <v>A0059.jpg</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>17</v>
@@ -3248,15 +3393,15 @@
         <v>A0060.jpg</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>17</v>
@@ -3278,15 +3423,15 @@
         <v>A0061.jpg</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>17</v>
@@ -3308,15 +3453,15 @@
         <v>A0062.jpg</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>17</v>
@@ -3338,15 +3483,15 @@
         <v>A0063.jpg</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>17</v>
@@ -3368,15 +3513,15 @@
         <v>A0064.jpg</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>17</v>
@@ -3398,15 +3543,15 @@
         <v>A0065.jpg</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>17</v>
@@ -3428,15 +3573,15 @@
         <v>A0066.jpg</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>17</v>
@@ -3458,15 +3603,15 @@
         <v>A0067.jpg</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>17</v>
@@ -3488,15 +3633,15 @@
         <v>A0068.jpg</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>17</v>
@@ -3518,15 +3663,15 @@
         <v>A0069.jpg</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>17</v>
@@ -3548,15 +3693,15 @@
         <v>A0070.jpg</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>17</v>
@@ -3578,15 +3723,15 @@
         <v>A0071.jpg</v>
       </c>
       <c r="I74" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>17</v>
@@ -3608,15 +3753,15 @@
         <v>A0072.jpg</v>
       </c>
       <c r="I75" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>17</v>
@@ -3638,15 +3783,15 @@
         <v>A0073.jpg</v>
       </c>
       <c r="I76" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>17</v>
@@ -3668,15 +3813,15 @@
         <v>A0074.jpg</v>
       </c>
       <c r="I77" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>17</v>
@@ -3698,15 +3843,15 @@
         <v>A0075.jpg</v>
       </c>
       <c r="I78" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>17</v>
@@ -3728,15 +3873,15 @@
         <v>A0076.jpg</v>
       </c>
       <c r="I79" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>17</v>
@@ -3758,15 +3903,15 @@
         <v>A0077.jpg</v>
       </c>
       <c r="I80" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>17</v>
@@ -3788,15 +3933,15 @@
         <v>A0078.jpg</v>
       </c>
       <c r="I81" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>17</v>
@@ -3814,19 +3959,19 @@
         <v>120</v>
       </c>
       <c r="H82" t="str">
-        <f t="shared" ref="H82:H137" si="1">_xlfn.CONCAT(A82,".jpg")</f>
+        <f t="shared" ref="H82:H145" si="1">_xlfn.CONCAT(A82,".jpg")</f>
         <v>A0135.jpg</v>
       </c>
       <c r="I82" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>17</v>
@@ -3848,15 +3993,15 @@
         <v>A0079.jpg</v>
       </c>
       <c r="I83" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>17</v>
@@ -3878,15 +4023,15 @@
         <v>A0080.jpg</v>
       </c>
       <c r="I84" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>17</v>
@@ -3908,15 +4053,15 @@
         <v>A0081.jpg</v>
       </c>
       <c r="I85" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>17</v>
@@ -3938,15 +4083,15 @@
         <v>A0082.jpg</v>
       </c>
       <c r="I86" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>17</v>
@@ -3968,15 +4113,15 @@
         <v>A0083.jpg</v>
       </c>
       <c r="I87" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>17</v>
@@ -3998,15 +4143,15 @@
         <v>A0084.jpg</v>
       </c>
       <c r="I88" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>17</v>
@@ -4028,15 +4173,15 @@
         <v>A0085.jpg</v>
       </c>
       <c r="I89" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>17</v>
@@ -4058,15 +4203,15 @@
         <v>A0086.jpg</v>
       </c>
       <c r="I90" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>17</v>
@@ -4088,15 +4233,15 @@
         <v>A0087.jpg</v>
       </c>
       <c r="I91" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>17</v>
@@ -4118,15 +4263,15 @@
         <v>A0088.jpg</v>
       </c>
       <c r="I92" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="2">
@@ -4146,15 +4291,15 @@
         <v>A0089.jpg</v>
       </c>
       <c r="I93" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="2">
@@ -4174,15 +4319,15 @@
         <v>A0090.jpg</v>
       </c>
       <c r="I94" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="2">
@@ -4202,15 +4347,15 @@
         <v>A0091.jpg</v>
       </c>
       <c r="I95" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="2">
@@ -4230,15 +4375,15 @@
         <v>A0092.jpg</v>
       </c>
       <c r="I96" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="2">
@@ -4258,15 +4403,15 @@
         <v>A0093.jpg</v>
       </c>
       <c r="I97" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="2">
@@ -4286,15 +4431,15 @@
         <v>A0094.jpg</v>
       </c>
       <c r="I98" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="2">
@@ -4314,15 +4459,15 @@
         <v>A0095.jpg</v>
       </c>
       <c r="I99" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>17</v>
@@ -4344,15 +4489,15 @@
         <v>A0096.jpg</v>
       </c>
       <c r="I100" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>17</v>
@@ -4374,15 +4519,15 @@
         <v>A0097.jpg</v>
       </c>
       <c r="I101" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>17</v>
@@ -4404,15 +4549,15 @@
         <v>A0098.jpg</v>
       </c>
       <c r="I102" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>17</v>
@@ -4434,15 +4579,15 @@
         <v>A0099.jpg</v>
       </c>
       <c r="I103" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>17</v>
@@ -4464,15 +4609,15 @@
         <v>A0100.jpg</v>
       </c>
       <c r="I104" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>17</v>
@@ -4494,15 +4639,15 @@
         <v>A0101.jpg</v>
       </c>
       <c r="I105" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>17</v>
@@ -4524,15 +4669,15 @@
         <v>A0102.jpg</v>
       </c>
       <c r="I106" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>17</v>
@@ -4554,15 +4699,15 @@
         <v>A0103.jpg</v>
       </c>
       <c r="I107" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>17</v>
@@ -4584,15 +4729,15 @@
         <v>A0104.jpg</v>
       </c>
       <c r="I108" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>17</v>
@@ -4614,15 +4759,15 @@
         <v>A0105.jpg</v>
       </c>
       <c r="I109" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>17</v>
@@ -4644,15 +4789,15 @@
         <v>A0106.jpg</v>
       </c>
       <c r="I110" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>17</v>
@@ -4674,15 +4819,15 @@
         <v>A0107.jpg</v>
       </c>
       <c r="I111" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>17</v>
@@ -4704,15 +4849,15 @@
         <v>A0108.jpg</v>
       </c>
       <c r="I112" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>17</v>
@@ -4734,15 +4879,15 @@
         <v>A0109.jpg</v>
       </c>
       <c r="I113" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>17</v>
@@ -4764,15 +4909,15 @@
         <v>A0110.jpg</v>
       </c>
       <c r="I114" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>17</v>
@@ -4794,15 +4939,15 @@
         <v>A0111.jpg</v>
       </c>
       <c r="I115" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>17</v>
@@ -4824,15 +4969,15 @@
         <v>A0112.jpg</v>
       </c>
       <c r="I116" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>17</v>
@@ -4854,15 +4999,15 @@
         <v>A0136.jpg</v>
       </c>
       <c r="I117" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>17</v>
@@ -4884,15 +5029,15 @@
         <v>A0113.jpg</v>
       </c>
       <c r="I118" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>17</v>
@@ -4914,15 +5059,15 @@
         <v>A0114.jpg</v>
       </c>
       <c r="I119" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>17</v>
@@ -4944,15 +5089,15 @@
         <v>A0115.jpg</v>
       </c>
       <c r="I120" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>17</v>
@@ -4974,15 +5119,15 @@
         <v>A0116.jpg</v>
       </c>
       <c r="I121" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>17</v>
@@ -5004,15 +5149,15 @@
         <v>A0117.jpg</v>
       </c>
       <c r="I122" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>17</v>
@@ -5034,15 +5179,15 @@
         <v>A0118.jpg</v>
       </c>
       <c r="I123" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>17</v>
@@ -5064,15 +5209,15 @@
         <v>A0119.jpg</v>
       </c>
       <c r="I124" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>17</v>
@@ -5094,15 +5239,15 @@
         <v>A0120.jpg</v>
       </c>
       <c r="I125" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>17</v>
@@ -5124,15 +5269,15 @@
         <v>A0121.jpg</v>
       </c>
       <c r="I126" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>17</v>
@@ -5154,15 +5299,15 @@
         <v>A0122.jpg</v>
       </c>
       <c r="I127" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>17</v>
@@ -5184,15 +5329,15 @@
         <v>A0123.jpg</v>
       </c>
       <c r="I128" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>17</v>
@@ -5214,15 +5359,15 @@
         <v>A0124.jpg</v>
       </c>
       <c r="I129" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>17</v>
@@ -5244,15 +5389,15 @@
         <v>A0125.jpg</v>
       </c>
       <c r="I130" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>17</v>
@@ -5274,15 +5419,15 @@
         <v>A0126.jpg</v>
       </c>
       <c r="I131" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>17</v>
@@ -5304,15 +5449,15 @@
         <v>A0127.jpg</v>
       </c>
       <c r="I132" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>17</v>
@@ -5334,15 +5479,15 @@
         <v>A0128.jpg</v>
       </c>
       <c r="I133" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>17</v>
@@ -5364,15 +5509,15 @@
         <v>A0129.jpg</v>
       </c>
       <c r="I134" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>17</v>
@@ -5394,15 +5539,15 @@
         <v>A0130.jpg</v>
       </c>
       <c r="I135" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>17</v>
@@ -5424,15 +5569,15 @@
         <v>A0131.jpg</v>
       </c>
       <c r="I136" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>17</v>
@@ -5454,7 +5599,577 @@
         <v>A0132.jpg</v>
       </c>
       <c r="I137" t="s">
-        <v>50</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>298</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" s="14">
+        <v>560</v>
+      </c>
+      <c r="E138" s="13">
+        <v>12</v>
+      </c>
+      <c r="F138" s="13">
+        <v>12</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v>A0137.jpg</v>
+      </c>
+      <c r="I138" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>299</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" s="11">
+        <v>4600</v>
+      </c>
+      <c r="E139" s="12">
+        <v>1</v>
+      </c>
+      <c r="F139" s="12">
+        <v>1</v>
+      </c>
+      <c r="G139">
+        <v>100</v>
+      </c>
+      <c r="H139" t="str">
+        <f t="shared" si="1"/>
+        <v>A0138.jpg</v>
+      </c>
+      <c r="I139" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>300</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140" s="11">
+        <v>300</v>
+      </c>
+      <c r="E140" s="12">
+        <v>10</v>
+      </c>
+      <c r="F140" s="12">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>100</v>
+      </c>
+      <c r="H140" t="str">
+        <f t="shared" si="1"/>
+        <v>A0139.jpg</v>
+      </c>
+      <c r="I140" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>301</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141" s="15">
+        <v>0</v>
+      </c>
+      <c r="E141" s="12">
+        <v>0</v>
+      </c>
+      <c r="F141" s="12">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141" t="str">
+        <f t="shared" si="1"/>
+        <v>A0140.jpg</v>
+      </c>
+      <c r="I141" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>302</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D142">
+        <v>64</v>
+      </c>
+      <c r="E142">
+        <v>36</v>
+      </c>
+      <c r="F142">
+        <v>36</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142" t="str">
+        <f t="shared" si="1"/>
+        <v>A0141.jpg</v>
+      </c>
+      <c r="I142" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>303</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143">
+        <v>105</v>
+      </c>
+      <c r="E143">
+        <v>24</v>
+      </c>
+      <c r="F143">
+        <v>24</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143" t="str">
+        <f t="shared" si="1"/>
+        <v>A0142.jpg</v>
+      </c>
+      <c r="I143" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>311</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144">
+        <v>130</v>
+      </c>
+      <c r="E144">
+        <v>25</v>
+      </c>
+      <c r="F144">
+        <v>25</v>
+      </c>
+      <c r="G144">
+        <v>100</v>
+      </c>
+      <c r="H144" t="str">
+        <f t="shared" si="1"/>
+        <v>A0143.jpg</v>
+      </c>
+      <c r="I144" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>312</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D145">
+        <v>510</v>
+      </c>
+      <c r="E145">
+        <v>10</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>100</v>
+      </c>
+      <c r="H145" t="str">
+        <f t="shared" si="1"/>
+        <v>A0144.jpg</v>
+      </c>
+      <c r="I145" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>313</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146">
+        <v>510</v>
+      </c>
+      <c r="E146">
+        <v>10</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146">
+        <v>100</v>
+      </c>
+      <c r="H146" t="str">
+        <f t="shared" ref="H146:H160" si="2">_xlfn.CONCAT(A146,".jpg")</f>
+        <v>A0145.jpg</v>
+      </c>
+      <c r="I146" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>314</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147">
+        <v>1200</v>
+      </c>
+      <c r="E147">
+        <v>5</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="G147">
+        <v>100</v>
+      </c>
+      <c r="H147" t="str">
+        <f t="shared" si="2"/>
+        <v>A0146.jpg</v>
+      </c>
+      <c r="I147" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>315</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148">
+        <v>460</v>
+      </c>
+      <c r="E148" s="15">
+        <v>0</v>
+      </c>
+      <c r="F148" s="15">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148" t="str">
+        <f t="shared" si="2"/>
+        <v>A0147.jpg</v>
+      </c>
+      <c r="I148" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>321</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149">
+        <v>75</v>
+      </c>
+      <c r="E149">
+        <v>24</v>
+      </c>
+      <c r="F149">
+        <v>24</v>
+      </c>
+      <c r="G149">
+        <v>100</v>
+      </c>
+      <c r="H149" t="str">
+        <f t="shared" si="2"/>
+        <v>A0148.jpg</v>
+      </c>
+      <c r="I149" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>329</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="15">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150" t="str">
+        <f t="shared" si="2"/>
+        <v>A0149.jpg</v>
+      </c>
+      <c r="I150" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>330</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151">
+        <v>1275</v>
+      </c>
+      <c r="E151">
+        <v>1</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>100</v>
+      </c>
+      <c r="H151" t="str">
+        <f t="shared" si="2"/>
+        <v>A0150.jpg</v>
+      </c>
+      <c r="I151" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>331</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152">
+        <v>3000</v>
+      </c>
+      <c r="E152">
+        <v>1</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152">
+        <v>100</v>
+      </c>
+      <c r="H152" t="str">
+        <f t="shared" si="2"/>
+        <v>A0151.jpg</v>
+      </c>
+      <c r="I152" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>332</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153">
+        <v>1580</v>
+      </c>
+      <c r="E153">
+        <v>12</v>
+      </c>
+      <c r="F153">
+        <v>12</v>
+      </c>
+      <c r="G153">
+        <v>100</v>
+      </c>
+      <c r="H153" t="str">
+        <f t="shared" si="2"/>
+        <v>A0152.jpg</v>
+      </c>
+      <c r="I153" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>333</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154">
+        <v>210</v>
+      </c>
+      <c r="E154">
+        <v>10</v>
+      </c>
+      <c r="F154">
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <v>100</v>
+      </c>
+      <c r="H154" t="str">
+        <f t="shared" si="2"/>
+        <v>A0153.jpg</v>
+      </c>
+      <c r="I154" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>334</v>
+      </c>
+      <c r="B155" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155">
+        <v>660</v>
+      </c>
+      <c r="E155">
+        <v>6</v>
+      </c>
+      <c r="F155">
+        <v>6</v>
+      </c>
+      <c r="G155">
+        <v>100</v>
+      </c>
+      <c r="H155" t="str">
+        <f t="shared" si="2"/>
+        <v>A0154.jpg</v>
+      </c>
+      <c r="I155" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>335</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156">
+        <v>1600</v>
+      </c>
+      <c r="E156">
+        <v>5</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156">
+        <v>100</v>
+      </c>
+      <c r="H156" t="str">
+        <f t="shared" si="2"/>
+        <v>A0155.jpg</v>
+      </c>
+      <c r="I156" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucil\Desktop\rmkits-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/064937db6ab52f6d/Desktop/web_carrito/rmkits/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25564EA4-A796-44CA-913D-60037C28D03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{25564EA4-A796-44CA-913D-60037C28D03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F878A076-516C-47E6-AAA0-D31183725283}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="1460" windowWidth="8860" windowHeight="9820" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1164,7 +1164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1188,19 +1188,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1522,15 +1516,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B0D8A5A-108C-466C-953C-70B57E87E4C5}">
   <dimension ref="A1:I156"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" customWidth="1"/>
-    <col min="2" max="2" width="39.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.36328125" customWidth="1"/>
-    <col min="9" max="9" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1559,7 +1553,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1570,7 +1564,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="5">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E2" s="5">
         <v>12</v>
@@ -1588,7 +1582,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1617,7 +1611,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1646,7 +1640,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1675,7 +1669,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1704,7 +1698,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1733,7 +1727,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1762,7 +1756,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -1791,7 +1785,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1820,7 +1814,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>64</v>
       </c>
@@ -1849,7 +1843,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -1878,7 +1872,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -1907,7 +1901,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -1936,7 +1930,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -1965,7 +1959,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -1994,7 +1988,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -2024,7 +2018,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -2054,7 +2048,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -2084,7 +2078,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>73</v>
       </c>
@@ -2114,7 +2108,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>111</v>
       </c>
@@ -2144,7 +2138,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>74</v>
       </c>
@@ -2174,7 +2168,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>75</v>
       </c>
@@ -2204,7 +2198,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -2234,7 +2228,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>77</v>
       </c>
@@ -2264,7 +2258,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>78</v>
       </c>
@@ -2294,7 +2288,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -2324,7 +2318,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -2354,7 +2348,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -2384,7 +2378,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -2414,7 +2408,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>83</v>
       </c>
@@ -2444,7 +2438,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>84</v>
       </c>
@@ -2474,7 +2468,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>97</v>
       </c>
@@ -2504,7 +2498,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>98</v>
       </c>
@@ -2534,7 +2528,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>99</v>
       </c>
@@ -2564,7 +2558,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>100</v>
       </c>
@@ -2594,7 +2588,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>101</v>
       </c>
@@ -2624,7 +2618,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>102</v>
       </c>
@@ -2654,7 +2648,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>103</v>
       </c>
@@ -2684,7 +2678,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>104</v>
       </c>
@@ -2714,7 +2708,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>105</v>
       </c>
@@ -2744,7 +2738,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>106</v>
       </c>
@@ -2774,7 +2768,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>107</v>
       </c>
@@ -2804,7 +2798,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>108</v>
       </c>
@@ -2834,7 +2828,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>271</v>
       </c>
@@ -2862,7 +2856,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>273</v>
       </c>
@@ -2890,7 +2884,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>109</v>
       </c>
@@ -2920,7 +2914,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>110</v>
       </c>
@@ -2950,7 +2944,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>112</v>
       </c>
@@ -2978,7 +2972,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>163</v>
       </c>
@@ -3006,7 +3000,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>164</v>
       </c>
@@ -3036,7 +3030,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>165</v>
       </c>
@@ -3066,7 +3060,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>166</v>
       </c>
@@ -3096,7 +3090,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>167</v>
       </c>
@@ -3126,7 +3120,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>168</v>
       </c>
@@ -3156,7 +3150,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>169</v>
       </c>
@@ -3186,7 +3180,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>170</v>
       </c>
@@ -3216,7 +3210,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -3246,7 +3240,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="26" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>172</v>
       </c>
@@ -3257,7 +3251,7 @@
         <v>17</v>
       </c>
       <c r="D59" s="7">
-        <v>1700</v>
+        <v>2520</v>
       </c>
       <c r="E59" s="7">
         <v>12</v>
@@ -3276,7 +3270,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>173</v>
       </c>
@@ -3306,7 +3300,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -3336,7 +3330,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>175</v>
       </c>
@@ -3366,7 +3360,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>176</v>
       </c>
@@ -3396,7 +3390,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>177</v>
       </c>
@@ -3426,7 +3420,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>178</v>
       </c>
@@ -3456,7 +3450,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>179</v>
       </c>
@@ -3486,7 +3480,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>180</v>
       </c>
@@ -3516,7 +3510,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>181</v>
       </c>
@@ -3546,7 +3540,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>182</v>
       </c>
@@ -3576,7 +3570,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>183</v>
       </c>
@@ -3606,7 +3600,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>184</v>
       </c>
@@ -3636,7 +3630,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>185</v>
       </c>
@@ -3666,7 +3660,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>186</v>
       </c>
@@ -3696,7 +3690,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>187</v>
       </c>
@@ -3726,7 +3720,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>188</v>
       </c>
@@ -3756,7 +3750,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>189</v>
       </c>
@@ -3786,7 +3780,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>190</v>
       </c>
@@ -3816,7 +3810,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>191</v>
       </c>
@@ -3846,7 +3840,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>192</v>
       </c>
@@ -3876,7 +3870,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>193</v>
       </c>
@@ -3906,7 +3900,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>194</v>
       </c>
@@ -3936,7 +3930,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>281</v>
       </c>
@@ -3966,7 +3960,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>195</v>
       </c>
@@ -3996,7 +3990,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>196</v>
       </c>
@@ -4026,7 +4020,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>197</v>
       </c>
@@ -4056,7 +4050,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>198</v>
       </c>
@@ -4086,7 +4080,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>199</v>
       </c>
@@ -4116,11 +4110,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>200</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C88" s="1" t="s">
@@ -4146,7 +4140,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>201</v>
       </c>
@@ -4176,7 +4170,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>202</v>
       </c>
@@ -4206,7 +4200,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>203</v>
       </c>
@@ -4236,7 +4230,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>204</v>
       </c>
@@ -4266,7 +4260,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>205</v>
       </c>
@@ -4294,7 +4288,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>206</v>
       </c>
@@ -4322,7 +4316,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>207</v>
       </c>
@@ -4350,7 +4344,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>208</v>
       </c>
@@ -4378,7 +4372,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>209</v>
       </c>
@@ -4406,7 +4400,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>210</v>
       </c>
@@ -4434,7 +4428,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>211</v>
       </c>
@@ -4462,7 +4456,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>212</v>
       </c>
@@ -4492,7 +4486,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>213</v>
       </c>
@@ -4522,7 +4516,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>214</v>
       </c>
@@ -4552,7 +4546,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>215</v>
       </c>
@@ -4582,7 +4576,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>216</v>
       </c>
@@ -4612,7 +4606,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>217</v>
       </c>
@@ -4642,7 +4636,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>218</v>
       </c>
@@ -4672,7 +4666,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -4702,7 +4696,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>220</v>
       </c>
@@ -4732,7 +4726,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>221</v>
       </c>
@@ -4762,7 +4756,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>222</v>
       </c>
@@ -4792,7 +4786,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>223</v>
       </c>
@@ -4822,7 +4816,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>224</v>
       </c>
@@ -4852,7 +4846,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>225</v>
       </c>
@@ -4882,7 +4876,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>226</v>
       </c>
@@ -4912,7 +4906,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>227</v>
       </c>
@@ -4942,7 +4936,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>228</v>
       </c>
@@ -4972,7 +4966,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>292</v>
       </c>
@@ -5002,7 +4996,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>229</v>
       </c>
@@ -5032,7 +5026,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>230</v>
       </c>
@@ -5062,7 +5056,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>231</v>
       </c>
@@ -5092,7 +5086,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>232</v>
       </c>
@@ -5122,7 +5116,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>233</v>
       </c>
@@ -5152,7 +5146,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>234</v>
       </c>
@@ -5182,7 +5176,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>235</v>
       </c>
@@ -5212,7 +5206,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>236</v>
       </c>
@@ -5242,7 +5236,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>237</v>
       </c>
@@ -5272,7 +5266,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>238</v>
       </c>
@@ -5302,7 +5296,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>239</v>
       </c>
@@ -5332,7 +5326,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>240</v>
       </c>
@@ -5362,7 +5356,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>241</v>
       </c>
@@ -5392,7 +5386,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>242</v>
       </c>
@@ -5422,7 +5416,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>243</v>
       </c>
@@ -5452,7 +5446,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>244</v>
       </c>
@@ -5482,7 +5476,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>245</v>
       </c>
@@ -5512,7 +5506,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>246</v>
       </c>
@@ -5542,7 +5536,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>247</v>
       </c>
@@ -5572,7 +5566,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>248</v>
       </c>
@@ -5602,29 +5596,29 @@
         <v>49</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>298</v>
       </c>
-      <c r="B138" s="10" t="s">
+      <c r="B138" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="C138" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D138" s="14">
+      <c r="C138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" s="12">
         <v>560</v>
       </c>
-      <c r="E138" s="13">
-        <v>12</v>
-      </c>
-      <c r="F138" s="13">
+      <c r="E138" s="8">
+        <v>12</v>
+      </c>
+      <c r="F138" s="8">
         <v>12</v>
       </c>
       <c r="G138">
         <v>0</v>
       </c>
-      <c r="H138" s="15" t="str">
+      <c r="H138" s="13" t="str">
         <f t="shared" si="1"/>
         <v>A0137.jpg</v>
       </c>
@@ -5632,23 +5626,23 @@
         <v>49</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>299</v>
       </c>
-      <c r="B139" s="10" t="s">
+      <c r="B139" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="C139" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D139" s="11">
+      <c r="C139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" s="10">
         <v>4600</v>
       </c>
-      <c r="E139" s="12">
+      <c r="E139" s="11">
         <v>1</v>
       </c>
-      <c r="F139" s="12">
+      <c r="F139" s="11">
         <v>1</v>
       </c>
       <c r="G139">
@@ -5662,23 +5656,23 @@
         <v>49</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>300</v>
       </c>
-      <c r="B140" s="10" t="s">
+      <c r="B140" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="C140" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D140" s="11">
+      <c r="C140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140" s="10">
         <v>300</v>
       </c>
-      <c r="E140" s="12">
+      <c r="E140" s="11">
         <v>10</v>
       </c>
-      <c r="F140" s="12">
+      <c r="F140" s="11">
         <v>1</v>
       </c>
       <c r="G140">
@@ -5692,23 +5686,23 @@
         <v>49</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>301</v>
       </c>
-      <c r="B141" s="10" t="s">
+      <c r="B141" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="C141" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D141" s="15">
+      <c r="C141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141" s="13">
         <v>0</v>
       </c>
-      <c r="E141" s="12">
+      <c r="E141" s="11">
         <v>0</v>
       </c>
-      <c r="F141" s="12">
+      <c r="F141" s="11">
         <v>0</v>
       </c>
       <c r="G141">
@@ -5722,14 +5716,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>302</v>
       </c>
-      <c r="B142" s="10" t="s">
+      <c r="B142" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="C142" s="10" t="s">
+      <c r="C142" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D142">
@@ -5752,14 +5746,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>303</v>
       </c>
-      <c r="B143" s="10" t="s">
+      <c r="B143" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="C143" s="10" t="s">
+      <c r="C143" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D143">
@@ -5782,14 +5776,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>311</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B144" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C144" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D144">
@@ -5812,14 +5806,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>312</v>
       </c>
-      <c r="B145" s="10" t="s">
+      <c r="B145" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="C145" s="10" t="s">
+      <c r="C145" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D145">
@@ -5842,14 +5836,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>313</v>
       </c>
-      <c r="B146" s="10" t="s">
+      <c r="B146" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="C146" s="10" t="s">
+      <c r="C146" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D146">
@@ -5865,21 +5859,21 @@
         <v>100</v>
       </c>
       <c r="H146" t="str">
-        <f t="shared" ref="H146:H160" si="2">_xlfn.CONCAT(A146,".jpg")</f>
+        <f t="shared" ref="H146:H156" si="2">_xlfn.CONCAT(A146,".jpg")</f>
         <v>A0145.jpg</v>
       </c>
       <c r="I146" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>314</v>
       </c>
-      <c r="B147" s="10" t="s">
+      <c r="B147" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="C147" s="10" t="s">
+      <c r="C147" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D147">
@@ -5902,23 +5896,23 @@
         <v>49</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>315</v>
       </c>
-      <c r="B148" s="10" t="s">
+      <c r="B148" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="C148" s="10" t="s">
+      <c r="C148" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D148">
         <v>460</v>
       </c>
-      <c r="E148" s="15">
+      <c r="E148" s="13">
         <v>0</v>
       </c>
-      <c r="F148" s="15">
+      <c r="F148" s="13">
         <v>0</v>
       </c>
       <c r="G148">
@@ -5932,14 +5926,14 @@
         <v>48</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>321</v>
       </c>
-      <c r="B149" s="10" t="s">
+      <c r="B149" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="C149" s="10" t="s">
+      <c r="C149" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D149">
@@ -5962,17 +5956,17 @@
         <v>49</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>329</v>
       </c>
-      <c r="B150" s="10" t="s">
+      <c r="B150" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="C150" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D150" s="15">
+      <c r="C150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="13">
         <v>0</v>
       </c>
       <c r="E150">
@@ -5992,14 +5986,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>330</v>
       </c>
-      <c r="B151" s="10" t="s">
+      <c r="B151" s="9" t="s">
         <v>322</v>
       </c>
-      <c r="C151" s="10" t="s">
+      <c r="C151" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D151">
@@ -6022,14 +6016,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>331</v>
       </c>
-      <c r="B152" s="10" t="s">
+      <c r="B152" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="C152" s="10" t="s">
+      <c r="C152" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D152">
@@ -6052,14 +6046,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>332</v>
       </c>
-      <c r="B153" s="10" t="s">
+      <c r="B153" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C153" s="10" t="s">
+      <c r="C153" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D153">
@@ -6072,7 +6066,7 @@
         <v>12</v>
       </c>
       <c r="G153">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H153" t="str">
         <f t="shared" si="2"/>
@@ -6082,14 +6076,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>333</v>
       </c>
-      <c r="B154" s="10" t="s">
+      <c r="B154" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="C154" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D154">
@@ -6112,14 +6106,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>334</v>
       </c>
-      <c r="B155" s="10" t="s">
+      <c r="B155" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="C155" s="10" t="s">
+      <c r="C155" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D155">
@@ -6142,14 +6136,14 @@
         <v>49</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>335</v>
       </c>
-      <c r="B156" s="10" t="s">
+      <c r="B156" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="C156" s="10" t="s">
+      <c r="C156" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D156">

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/064937db6ab52f6d/Desktop/web_carrito/rmkits/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{25564EA4-A796-44CA-913D-60037C28D03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F878A076-516C-47E6-AAA0-D31183725283}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{25564EA4-A796-44CA-913D-60037C28D03E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4EA6408-65BC-4693-B90E-07B7DA3243FE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
+    <workbookView xWindow="3705" yWindow="435" windowWidth="15375" windowHeight="7785" xr2:uid="{C4B6B2E4-7AFF-45F0-BE4D-6E6AB0ED2031}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="344">
   <si>
     <t>codigo</t>
   </si>
@@ -90,9 +90,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Cinta correctora Filgo 12mts</t>
-  </si>
-  <si>
     <t>A005</t>
   </si>
   <si>
@@ -297,9 +294,6 @@
     <t>Crayones Filgo x12 colores</t>
   </si>
   <si>
-    <t>Crayones Filgo x12 colores Fluo</t>
-  </si>
-  <si>
     <t>Lápices Tonos de Piel Filgo x6 colores</t>
   </si>
   <si>
@@ -1048,13 +1042,37 @@
   </si>
   <si>
     <t>Corrector liquido Filgo 012</t>
+  </si>
+  <si>
+    <t>repuesto</t>
+  </si>
+  <si>
+    <t>lapicera borrax se filgo borrable</t>
+  </si>
+  <si>
+    <t>repuesto lapicera borrax se</t>
+  </si>
+  <si>
+    <t>boligrafo nero negro retactil filgo</t>
+  </si>
+  <si>
+    <t>boligrafo nero azul retactil filgo</t>
+  </si>
+  <si>
+    <t>Voligoma 30ml</t>
+  </si>
+  <si>
+    <t>Lapices intro x12 largos</t>
+  </si>
+  <si>
+    <t>Crayones Filgo x6 colores Fluo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1074,8 +1092,16 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1085,6 +1111,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1164,7 +1214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1201,6 +1251,12 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1515,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B0D8A5A-108C-466C-953C-70B57E87E4C5}">
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I163"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
@@ -1550,15 +1606,15 @@
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>336</v>
+      <c r="B2" s="14" t="s">
+        <v>334</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>16</v>
@@ -1579,15 +1635,15 @@
         <v>12</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>337</v>
+      <c r="B3" s="14" t="s">
+        <v>335</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>17</v>
@@ -1608,21 +1664,21 @@
         <v>13</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>18</v>
+      <c r="B4" s="14" t="s">
+        <v>336</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="5">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E4" s="5">
         <v>12</v>
@@ -1637,15 +1693,15 @@
         <v>14</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>24</v>
+      <c r="B5" s="14" t="s">
+        <v>23</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>17</v>
@@ -1666,15 +1722,15 @@
         <v>15</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>24</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>17</v>
@@ -1692,18 +1748,18 @@
         <v>500</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>32</v>
+        <v>19</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>31</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>17</v>
@@ -1721,18 +1777,18 @@
         <v>5000</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>17</v>
@@ -1750,24 +1806,24 @@
         <v>5000</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="5">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="E9" s="5">
         <v>36</v>
@@ -1779,24 +1835,24 @@
         <v>1500</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>51</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="5">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="E10" s="5">
         <v>36</v>
@@ -1808,18 +1864,18 @@
         <v>1500</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>34</v>
+        <v>63</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>33</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>17</v>
@@ -1837,24 +1893,24 @@
         <v>2400</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>35</v>
+        <v>64</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="5">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E12" s="5">
         <v>6</v>
@@ -1863,27 +1919,27 @@
         <v>6</v>
       </c>
       <c r="G12" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>37</v>
+        <v>65</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>36</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="5">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E13" s="5">
         <v>6</v>
@@ -1895,24 +1951,24 @@
         <v>120</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>36</v>
+        <v>66</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>35</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="5">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="E14" s="5">
         <v>3</v>
@@ -1921,27 +1977,27 @@
         <v>3</v>
       </c>
       <c r="G14" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>38</v>
+        <v>67</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="5">
-        <v>285</v>
+        <v>350</v>
       </c>
       <c r="E15" s="5">
         <v>24</v>
@@ -1953,24 +2009,24 @@
         <v>2000</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>39</v>
+        <v>68</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>38</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="5">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E16" s="5">
         <v>24</v>
@@ -1982,24 +2038,24 @@
         <v>2000</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>60</v>
+        <v>69</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>59</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="5">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="E17" s="5">
         <v>12</v>
@@ -2015,21 +2071,21 @@
         <v>A0018.jpg</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>61</v>
+        <v>70</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>60</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="5">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="E18" s="5">
         <v>12</v>
@@ -2045,21 +2101,21 @@
         <v>A0019.jpg</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>62</v>
+        <v>71</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>61</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D19" s="5">
-        <v>2500</v>
+        <v>3300</v>
       </c>
       <c r="E19" s="5">
         <v>12</v>
@@ -2075,21 +2131,21 @@
         <v>A0020.jpg</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>63</v>
+        <v>72</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>62</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="5">
-        <v>4600</v>
+        <v>6200</v>
       </c>
       <c r="E20" s="5">
         <v>6</v>
@@ -2105,15 +2161,15 @@
         <v>A0021.jpg</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>88</v>
+        <v>109</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>86</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>17</v>
@@ -2135,21 +2191,21 @@
         <v>A0045.jpg</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>41</v>
+        <v>73</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>40</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="5">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E22" s="5">
         <v>24</v>
@@ -2165,21 +2221,21 @@
         <v>A0016.jpg</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>40</v>
+        <v>74</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="5">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E23" s="5">
         <v>12</v>
@@ -2195,21 +2251,21 @@
         <v>A0017.jpg</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>50</v>
+        <v>75</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>49</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="5">
-        <v>1400</v>
+        <v>1650</v>
       </c>
       <c r="E24" s="5">
         <v>12</v>
@@ -2225,21 +2281,21 @@
         <v>A0022.jpg</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>113</v>
+        <v>76</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>111</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D25" s="5">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="E25" s="5">
         <v>12</v>
@@ -2255,15 +2311,15 @@
         <v>A0023.jpg</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>53</v>
+        <v>77</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>17</v>
@@ -2285,21 +2341,21 @@
         <v>A0024.jpg</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>54</v>
+        <v>78</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="5">
-        <v>13500</v>
+        <v>15000</v>
       </c>
       <c r="E27" s="5">
         <v>12</v>
@@ -2315,21 +2371,21 @@
         <v>A0025.jpg</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>80</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>55</v>
+        <v>79</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D28" s="5">
-        <v>23000</v>
+        <v>26000</v>
       </c>
       <c r="E28" s="5">
         <v>8</v>
@@ -2345,21 +2401,21 @@
         <v>A0026.jpg</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>56</v>
+        <v>80</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>55</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D29" s="5">
-        <v>32500</v>
+        <v>36500</v>
       </c>
       <c r="E29" s="5">
         <v>6</v>
@@ -2375,21 +2431,21 @@
         <v>A0027.jpg</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>57</v>
+        <v>81</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="5">
-        <v>43800</v>
+        <v>49000</v>
       </c>
       <c r="E30" s="5">
         <v>3</v>
@@ -2405,21 +2461,21 @@
         <v>A0028.jpg</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>58</v>
+        <v>82</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="5">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E31" s="5">
         <v>12</v>
@@ -2435,21 +2491,21 @@
         <v>A0029.jpg</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="5">
-        <v>6480</v>
+        <v>7920</v>
       </c>
       <c r="E32" s="5">
         <v>1</v>
@@ -2465,21 +2521,21 @@
         <v>A0030.jpg</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>89</v>
+        <v>95</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>87</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D33" s="5">
-        <v>6480</v>
+        <v>7920</v>
       </c>
       <c r="E33" s="5">
         <v>1</v>
@@ -2495,15 +2551,15 @@
         <v>A0031.jpg</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>98</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>85</v>
+        <v>96</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>17</v>
@@ -2525,15 +2581,15 @@
         <v>A0032.jpg</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>99</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>86</v>
+        <v>97</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>17</v>
@@ -2555,21 +2611,21 @@
         <v>A0033.jpg</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>87</v>
+        <v>98</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>343</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D36" s="5">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="E36" s="5">
         <v>1</v>
@@ -2585,21 +2641,21 @@
         <v>A0034.jpg</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>101</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>90</v>
+        <v>99</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="5">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="E37" s="5">
         <v>36</v>
@@ -2615,21 +2671,21 @@
         <v>A0035.jpg</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>102</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>114</v>
+        <v>100</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D38" s="5">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="E38" s="5">
         <v>36</v>
@@ -2645,15 +2701,15 @@
         <v>A0036.jpg</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>17</v>
@@ -2675,15 +2731,15 @@
         <v>A0037.jpg</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>104</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>92</v>
+        <v>102</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>90</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>17</v>
@@ -2705,15 +2761,15 @@
         <v>A0038.jpg</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>105</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>93</v>
+        <v>103</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>91</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>17</v>
@@ -2735,21 +2791,21 @@
         <v>A0039.jpg</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>106</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>94</v>
+        <v>104</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>92</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="5">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="E42" s="5">
         <v>24</v>
@@ -2765,21 +2821,21 @@
         <v>A0040.jpg</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>107</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>95</v>
+        <v>105</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D43" s="5">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="E43" s="5">
         <v>24</v>
@@ -2795,21 +2851,21 @@
         <v>A0041.jpg</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D44" s="5">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="E44" s="5">
         <v>12</v>
@@ -2825,15 +2881,15 @@
         <v>A0042.jpg</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>271</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>270</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5">
@@ -2853,15 +2909,15 @@
         <v>A0133.jpg</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>273</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>272</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5">
@@ -2881,21 +2937,21 @@
         <v>A0134.jpg</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>109</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>275</v>
+        <v>107</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>273</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D47" s="5">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E47" s="5">
         <v>12</v>
@@ -2911,15 +2967,15 @@
         <v>A0043.jpg</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>110</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>276</v>
+        <v>108</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>274</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>17</v>
@@ -2941,15 +2997,15 @@
         <v>A0044.jpg</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C49" s="6"/>
       <c r="D49" s="7">
@@ -2969,15 +3025,15 @@
         <v>A0046.jpg</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="7">
@@ -2997,15 +3053,15 @@
         <v>A0047.jpg</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>17</v>
@@ -3027,15 +3083,15 @@
         <v>A0048.jpg</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>17</v>
@@ -3057,15 +3113,15 @@
         <v>A0049.jpg</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>17</v>
@@ -3087,15 +3143,15 @@
         <v>A0050.jpg</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>17</v>
@@ -3117,15 +3173,15 @@
         <v>A0051.jpg</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>17</v>
@@ -3147,15 +3203,15 @@
         <v>A0052.jpg</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>17</v>
@@ -3177,15 +3233,15 @@
         <v>A0053.jpg</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>17</v>
@@ -3207,15 +3263,15 @@
         <v>A0054.jpg</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>17</v>
@@ -3237,15 +3293,15 @@
         <v>A0055.jpg</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>17</v>
@@ -3267,15 +3323,15 @@
         <v>A0056.jpg</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>17</v>
@@ -3297,15 +3353,15 @@
         <v>A0057.jpg</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>17</v>
@@ -3327,15 +3383,15 @@
         <v>A0058.jpg</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>17</v>
@@ -3357,15 +3413,15 @@
         <v>A0059.jpg</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>17</v>
@@ -3387,15 +3443,15 @@
         <v>A0060.jpg</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>17</v>
@@ -3417,15 +3473,15 @@
         <v>A0061.jpg</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>17</v>
@@ -3447,15 +3503,15 @@
         <v>A0062.jpg</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>17</v>
@@ -3477,15 +3533,15 @@
         <v>A0063.jpg</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>17</v>
@@ -3507,15 +3563,15 @@
         <v>A0064.jpg</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>17</v>
@@ -3537,15 +3593,15 @@
         <v>A0065.jpg</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>17</v>
@@ -3567,15 +3623,15 @@
         <v>A0066.jpg</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>17</v>
@@ -3597,15 +3653,15 @@
         <v>A0067.jpg</v>
       </c>
       <c r="I70" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>17</v>
@@ -3627,15 +3683,15 @@
         <v>A0068.jpg</v>
       </c>
       <c r="I71" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>17</v>
@@ -3657,15 +3713,15 @@
         <v>A0069.jpg</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>17</v>
@@ -3687,15 +3743,15 @@
         <v>A0070.jpg</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>17</v>
@@ -3717,15 +3773,15 @@
         <v>A0071.jpg</v>
       </c>
       <c r="I74" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>17</v>
@@ -3747,15 +3803,15 @@
         <v>A0072.jpg</v>
       </c>
       <c r="I75" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>17</v>
@@ -3777,15 +3833,15 @@
         <v>A0073.jpg</v>
       </c>
       <c r="I76" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>17</v>
@@ -3807,15 +3863,15 @@
         <v>A0074.jpg</v>
       </c>
       <c r="I77" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>17</v>
@@ -3837,15 +3893,15 @@
         <v>A0075.jpg</v>
       </c>
       <c r="I78" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>17</v>
@@ -3867,15 +3923,15 @@
         <v>A0076.jpg</v>
       </c>
       <c r="I79" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>17</v>
@@ -3897,15 +3953,15 @@
         <v>A0077.jpg</v>
       </c>
       <c r="I80" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>17</v>
@@ -3927,15 +3983,15 @@
         <v>A0078.jpg</v>
       </c>
       <c r="I81" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>17</v>
@@ -3957,15 +4013,15 @@
         <v>A0135.jpg</v>
       </c>
       <c r="I82" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>17</v>
@@ -3987,15 +4043,15 @@
         <v>A0079.jpg</v>
       </c>
       <c r="I83" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>17</v>
@@ -4017,15 +4073,15 @@
         <v>A0080.jpg</v>
       </c>
       <c r="I84" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>17</v>
@@ -4047,15 +4103,15 @@
         <v>A0081.jpg</v>
       </c>
       <c r="I85" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>17</v>
@@ -4077,15 +4133,15 @@
         <v>A0082.jpg</v>
       </c>
       <c r="I86" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>17</v>
@@ -4107,15 +4163,15 @@
         <v>A0083.jpg</v>
       </c>
       <c r="I87" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>17</v>
@@ -4137,15 +4193,15 @@
         <v>A0084.jpg</v>
       </c>
       <c r="I88" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>17</v>
@@ -4167,15 +4223,15 @@
         <v>A0085.jpg</v>
       </c>
       <c r="I89" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>17</v>
@@ -4197,15 +4253,15 @@
         <v>A0086.jpg</v>
       </c>
       <c r="I90" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>17</v>
@@ -4227,15 +4283,15 @@
         <v>A0087.jpg</v>
       </c>
       <c r="I91" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>17</v>
@@ -4257,15 +4313,15 @@
         <v>A0088.jpg</v>
       </c>
       <c r="I92" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="2">
@@ -4285,15 +4341,15 @@
         <v>A0089.jpg</v>
       </c>
       <c r="I93" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="2">
@@ -4313,15 +4369,15 @@
         <v>A0090.jpg</v>
       </c>
       <c r="I94" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="2">
@@ -4341,15 +4397,15 @@
         <v>A0091.jpg</v>
       </c>
       <c r="I95" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="2">
@@ -4369,15 +4425,15 @@
         <v>A0092.jpg</v>
       </c>
       <c r="I96" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="2">
@@ -4397,15 +4453,15 @@
         <v>A0093.jpg</v>
       </c>
       <c r="I97" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="2">
@@ -4425,15 +4481,15 @@
         <v>A0094.jpg</v>
       </c>
       <c r="I98" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="2">
@@ -4453,15 +4509,15 @@
         <v>A0095.jpg</v>
       </c>
       <c r="I99" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>17</v>
@@ -4483,15 +4539,15 @@
         <v>A0096.jpg</v>
       </c>
       <c r="I100" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>17</v>
@@ -4513,15 +4569,15 @@
         <v>A0097.jpg</v>
       </c>
       <c r="I101" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>17</v>
@@ -4543,15 +4599,15 @@
         <v>A0098.jpg</v>
       </c>
       <c r="I102" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>17</v>
@@ -4573,15 +4629,15 @@
         <v>A0099.jpg</v>
       </c>
       <c r="I103" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>17</v>
@@ -4603,15 +4659,15 @@
         <v>A0100.jpg</v>
       </c>
       <c r="I104" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>17</v>
@@ -4633,15 +4689,15 @@
         <v>A0101.jpg</v>
       </c>
       <c r="I105" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>17</v>
@@ -4663,15 +4719,15 @@
         <v>A0102.jpg</v>
       </c>
       <c r="I106" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>17</v>
@@ -4693,15 +4749,15 @@
         <v>A0103.jpg</v>
       </c>
       <c r="I107" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>17</v>
@@ -4723,15 +4779,15 @@
         <v>A0104.jpg</v>
       </c>
       <c r="I108" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>17</v>
@@ -4753,15 +4809,15 @@
         <v>A0105.jpg</v>
       </c>
       <c r="I109" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>17</v>
@@ -4783,15 +4839,15 @@
         <v>A0106.jpg</v>
       </c>
       <c r="I110" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>17</v>
@@ -4813,15 +4869,15 @@
         <v>A0107.jpg</v>
       </c>
       <c r="I111" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>17</v>
@@ -4843,15 +4899,15 @@
         <v>A0108.jpg</v>
       </c>
       <c r="I112" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>17</v>
@@ -4873,15 +4929,15 @@
         <v>A0109.jpg</v>
       </c>
       <c r="I113" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>17</v>
@@ -4903,15 +4959,15 @@
         <v>A0110.jpg</v>
       </c>
       <c r="I114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>17</v>
@@ -4933,15 +4989,15 @@
         <v>A0111.jpg</v>
       </c>
       <c r="I115" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>17</v>
@@ -4963,15 +5019,15 @@
         <v>A0112.jpg</v>
       </c>
       <c r="I116" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>17</v>
@@ -4993,15 +5049,15 @@
         <v>A0136.jpg</v>
       </c>
       <c r="I117" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>17</v>
@@ -5023,15 +5079,15 @@
         <v>A0113.jpg</v>
       </c>
       <c r="I118" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>17</v>
@@ -5053,15 +5109,15 @@
         <v>A0114.jpg</v>
       </c>
       <c r="I119" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>17</v>
@@ -5083,15 +5139,15 @@
         <v>A0115.jpg</v>
       </c>
       <c r="I120" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>17</v>
@@ -5113,15 +5169,15 @@
         <v>A0116.jpg</v>
       </c>
       <c r="I121" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>17</v>
@@ -5143,15 +5199,15 @@
         <v>A0117.jpg</v>
       </c>
       <c r="I122" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>17</v>
@@ -5173,15 +5229,15 @@
         <v>A0118.jpg</v>
       </c>
       <c r="I123" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>17</v>
@@ -5203,15 +5259,15 @@
         <v>A0119.jpg</v>
       </c>
       <c r="I124" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>17</v>
@@ -5233,15 +5289,15 @@
         <v>A0120.jpg</v>
       </c>
       <c r="I125" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>17</v>
@@ -5263,15 +5319,15 @@
         <v>A0121.jpg</v>
       </c>
       <c r="I126" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>17</v>
@@ -5293,15 +5349,15 @@
         <v>A0122.jpg</v>
       </c>
       <c r="I127" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>17</v>
@@ -5323,15 +5379,15 @@
         <v>A0123.jpg</v>
       </c>
       <c r="I128" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>17</v>
@@ -5353,15 +5409,15 @@
         <v>A0124.jpg</v>
       </c>
       <c r="I129" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>17</v>
@@ -5383,15 +5439,15 @@
         <v>A0125.jpg</v>
       </c>
       <c r="I130" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>17</v>
@@ -5413,15 +5469,15 @@
         <v>A0126.jpg</v>
       </c>
       <c r="I131" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>17</v>
@@ -5443,15 +5499,15 @@
         <v>A0127.jpg</v>
       </c>
       <c r="I132" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>17</v>
@@ -5473,15 +5529,15 @@
         <v>A0128.jpg</v>
       </c>
       <c r="I133" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>17</v>
@@ -5503,15 +5559,15 @@
         <v>A0129.jpg</v>
       </c>
       <c r="I134" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>17</v>
@@ -5533,15 +5589,15 @@
         <v>A0130.jpg</v>
       </c>
       <c r="I135" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>17</v>
@@ -5563,15 +5619,15 @@
         <v>A0131.jpg</v>
       </c>
       <c r="I136" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>17</v>
@@ -5593,15 +5649,15 @@
         <v>A0132.jpg</v>
       </c>
       <c r="I137" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C138" s="9" t="s">
         <v>17</v>
@@ -5623,15 +5679,15 @@
         <v>A0137.jpg</v>
       </c>
       <c r="I138" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C139" s="9" t="s">
         <v>17</v>
@@ -5653,15 +5709,15 @@
         <v>A0138.jpg</v>
       </c>
       <c r="I139" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C140" s="9" t="s">
         <v>17</v>
@@ -5683,15 +5739,15 @@
         <v>A0139.jpg</v>
       </c>
       <c r="I140" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C141" s="9" t="s">
         <v>17</v>
@@ -5713,15 +5769,15 @@
         <v>A0140.jpg</v>
       </c>
       <c r="I141" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C142" s="9" t="s">
         <v>17</v>
@@ -5743,15 +5799,15 @@
         <v>A0141.jpg</v>
       </c>
       <c r="I142" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C143" s="9" t="s">
         <v>17</v>
@@ -5773,15 +5829,15 @@
         <v>A0142.jpg</v>
       </c>
       <c r="I143" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C144" s="9" t="s">
         <v>17</v>
@@ -5803,15 +5859,15 @@
         <v>A0143.jpg</v>
       </c>
       <c r="I144" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C145" s="9" t="s">
         <v>17</v>
@@ -5833,15 +5889,15 @@
         <v>A0144.jpg</v>
       </c>
       <c r="I145" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C146" s="9" t="s">
         <v>17</v>
@@ -5863,15 +5919,15 @@
         <v>A0145.jpg</v>
       </c>
       <c r="I146" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>312</v>
+      </c>
+      <c r="B147" s="9" t="s">
         <v>314</v>
-      </c>
-      <c r="B147" s="9" t="s">
-        <v>316</v>
       </c>
       <c r="C147" s="9" t="s">
         <v>17</v>
@@ -5893,15 +5949,15 @@
         <v>A0146.jpg</v>
       </c>
       <c r="I147" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>313</v>
+      </c>
+      <c r="B148" s="9" t="s">
         <v>315</v>
-      </c>
-      <c r="B148" s="9" t="s">
-        <v>317</v>
       </c>
       <c r="C148" s="9" t="s">
         <v>17</v>
@@ -5923,15 +5979,15 @@
         <v>A0147.jpg</v>
       </c>
       <c r="I148" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C149" s="9" t="s">
         <v>17</v>
@@ -5953,15 +6009,15 @@
         <v>A0148.jpg</v>
       </c>
       <c r="I149" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C150" s="9" t="s">
         <v>17</v>
@@ -5983,15 +6039,15 @@
         <v>A0149.jpg</v>
       </c>
       <c r="I150" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C151" s="9" t="s">
         <v>17</v>
@@ -6013,15 +6069,15 @@
         <v>A0150.jpg</v>
       </c>
       <c r="I151" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C152" s="9" t="s">
         <v>17</v>
@@ -6043,15 +6099,15 @@
         <v>A0151.jpg</v>
       </c>
       <c r="I152" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C153" s="9" t="s">
         <v>17</v>
@@ -6073,15 +6129,15 @@
         <v>A0152.jpg</v>
       </c>
       <c r="I153" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C154" s="9" t="s">
         <v>17</v>
@@ -6103,15 +6159,15 @@
         <v>A0153.jpg</v>
       </c>
       <c r="I154" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C155" s="9" t="s">
         <v>17</v>
@@ -6133,15 +6189,15 @@
         <v>A0154.jpg</v>
       </c>
       <c r="I155" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C156" s="9" t="s">
         <v>17</v>
@@ -6163,11 +6219,99 @@
         <v>A0155.jpg</v>
       </c>
       <c r="I156" t="s">
-        <v>49</v>
-      </c>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B157" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="D157">
+        <v>700</v>
+      </c>
+      <c r="E157">
+        <v>12</v>
+      </c>
+      <c r="F157">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B158" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="D158">
+        <v>300</v>
+      </c>
+      <c r="E158">
+        <v>12</v>
+      </c>
+      <c r="F158">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B159" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="D159">
+        <v>410</v>
+      </c>
+      <c r="E159">
+        <v>36</v>
+      </c>
+      <c r="F159">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B160" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="D160">
+        <v>410</v>
+      </c>
+      <c r="E160">
+        <v>36</v>
+      </c>
+      <c r="F160">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B161" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="D161">
+        <v>1100</v>
+      </c>
+      <c r="E161">
+        <v>12</v>
+      </c>
+      <c r="F161">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B162" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="D162">
+        <v>590</v>
+      </c>
+      <c r="E162">
+        <v>12</v>
+      </c>
+      <c r="F162">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B163" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>